--- a/ILLIA/Septiembre/ILLIA-Septiembre.xlsx
+++ b/ILLIA/Septiembre/ILLIA-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\ILLIA\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6E14AE-2678-428A-8776-2ED5B27A9EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC01ACE-655E-43EA-89C4-09BE1585F9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Copia de PRORRATEO'!$A$1:$Q$46</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$141</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$147</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="198">
   <si>
     <t>TELEFONO: 11 5320-2676</t>
   </si>
@@ -522,76 +522,106 @@
     <t>NOTA : ESTIMADOS PROPIETARIOS E INQUILINOS, NECESITAMOS QUE ABONEN LAS EXPENSAS ATRASADAS YA QUE ES NECESARIO ABONAR EN TIEMPO Y FORMA LOS GASTOS ORDINARIOS. ADEMAS, LES SOLICITAMOS AL PAGAR LAS EXPENSAS INFORMAR MEDIANTE MAIL O WHATSAPP JUNTO A LA UF Y COCHERA CORRESPONDIENTE AL PAGO. QUIENES NO INFORMEN LOS PAGOS CORREN EL RIESGO DE NO VER LOS MISMOS IMPUTADOS. LOS QUE TIENEN LINEAS GRISAS CORRESPONDEN A PLANES DE PAGO EN VIGENCIA.</t>
   </si>
   <si>
-    <t>VTO 15/09</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>Sueldo Ana encargada AGOSTO</t>
-  </si>
-  <si>
-    <t>Claudio Sosa Periodo AGOSTO</t>
-  </si>
-  <si>
-    <t>AGOSTO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Ascensores ADS - Mantenimiento de ascensor (Período AGOSTO)</t>
-  </si>
-  <si>
-    <t>AYSA - Mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>GASTOS BANCARIOS AGOSTO Y AGOSTO</t>
-  </si>
-  <si>
-    <t>Transf 12/08</t>
-  </si>
-  <si>
-    <t>Bazar - Los nenes - Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>Vallazza Gustavo - Limpieza y desinfeccion de tanques de agua potable, analisis y certificado correspondiente</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>Transf 13/08</t>
-  </si>
-  <si>
-    <t>Debito 05/08</t>
-  </si>
-  <si>
-    <t>Debito 23/08</t>
-  </si>
-  <si>
-    <t>Balcazza Leonardo Daniel - Colocacion de placas de durlocks faktantes - Baños 4A - 3A y Trabajo realizado en 6C</t>
-  </si>
-  <si>
-    <t>Transf 07/08 y 22/08</t>
-  </si>
-  <si>
-    <t>EDESUR - 30-65511651-2 - La factura viene en $0</t>
-  </si>
-  <si>
     <t>CONVENIO DE PAGO 1A: 12 CUOTAS MENSUALES DE $96.000 MAS EXPESAS EN CURSO. ADELANTO DE $200.000</t>
   </si>
   <si>
     <t>CONVENIO DE PAGO 6A: 8 CUOTAS MENSUALES DE $90.000 MAS EXPESAS EN CURSO. ADELANTO DE $200.000 (ABONO MES PASADO)</t>
   </si>
   <si>
-    <t>Roxana Goldemberg - Convenio Pago 1A - Abonado por UF</t>
-  </si>
-  <si>
-    <t>Roxana Goldemberg - Convenio Pago 6A - Abonado por UF</t>
-  </si>
-  <si>
-    <t>1 er cuota convenio de pago 6A</t>
+    <t>VTO 15/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Sueldo Ana encargada SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Claudio Sosa Periodo SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Ascensores ADS - Mantenimiento de ascensor (Período SEPTIEMBRE)</t>
+  </si>
+  <si>
+    <t>AYSA - Mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GASTOS BANCARIOS SEPTIEMBRE </t>
+  </si>
+  <si>
+    <t>Debito 03/09</t>
+  </si>
+  <si>
+    <t>Debito 05/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDESUR - 30-65511651-2 </t>
+  </si>
+  <si>
+    <t>Servisur  - Lampara techo piso 6</t>
+  </si>
+  <si>
+    <t>Transf 08/09</t>
+  </si>
+  <si>
+    <t>Transf 16/09</t>
+  </si>
+  <si>
+    <t>Julio doartero - Arreglo de mamposteria - pintura 5A</t>
+  </si>
+  <si>
+    <t>Julio doartero - Adelanto arreglo puerta blindex hall de entrada y vereda</t>
+  </si>
+  <si>
+    <t>Transf  22/09</t>
+  </si>
+  <si>
+    <t>Debito 24/09</t>
+  </si>
+  <si>
+    <t>Debito 12/09</t>
+  </si>
+  <si>
+    <t>Ascensores ADS - Suministro y colocacion nuevo contacto de cabina - Puerta piso 6</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Transf 05/09</t>
+  </si>
+  <si>
+    <t>Cerrajeria Juego de llaves administracion</t>
+  </si>
+  <si>
+    <t>Copia de llaves 5A - Gasto particular</t>
+  </si>
+  <si>
+    <t>Compra baldosas - Porcelanato Pulido Rectificado - 4 cajas</t>
+  </si>
+  <si>
+    <t>Envio de baldosas desde Munro</t>
+  </si>
+  <si>
+    <t>Transf 30/09</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>2 da cuota convenio de pago 6A</t>
+  </si>
+  <si>
+    <t>1 er cuota convenio de pago 1A</t>
+  </si>
+  <si>
+    <t>Carta documento doble cobrada a 5B</t>
   </si>
 </sst>
 </file>
@@ -599,15 +629,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="_-&quot;$&quot;\ * #,##0.0000_-;\-&quot;$&quot;\ * #,##0.0000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@"/>
   </numFmts>
   <fonts count="35" x14ac:knownFonts="1">
     <font>
@@ -1555,7 +1585,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27"/>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="27"/>
   </cellStyleXfs>
-  <cellXfs count="286">
+  <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1578,29 +1608,29 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1618,46 +1648,46 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1665,29 +1695,29 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1700,28 +1730,28 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
@@ -1730,7 +1760,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1740,12 +1770,12 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1761,24 +1791,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="28" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="27" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="16" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="14" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="14" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="14" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="14" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="14" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1787,28 +1814,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="19" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="19" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="31" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="31" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="27" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="32" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="27" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="27" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="27" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="28" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="28" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
@@ -1828,10 +1855,10 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1845,25 +1872,25 @@
     <xf numFmtId="0" fontId="21" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="19" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="19" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="19" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="19" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="19" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1882,15 +1909,70 @@
     <xf numFmtId="16" fontId="14" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="21" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="21" fillId="21" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="28" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1898,25 +1980,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1926,6 +2004,10 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1962,53 +2044,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="23" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="21" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="21" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="28" fillId="22" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="29" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="14" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2284,7 +2319,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1007"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.42578125" customWidth="1"/>
@@ -2302,51 +2337,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="208"/>
-      <c r="B1" s="209"/>
-      <c r="C1" s="210"/>
-      <c r="D1" s="210"/>
-      <c r="E1" s="211"/>
+      <c r="A1" s="207"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="209"/>
+      <c r="D1" s="209"/>
+      <c r="E1" s="210"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="212"/>
-      <c r="B2" s="213" t="s">
+      <c r="A2" s="211"/>
+      <c r="B2" s="212" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="214"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="213"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="212"/>
-      <c r="B3" s="227" t="s">
+      <c r="A3" s="211"/>
+      <c r="B3" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="228"/>
-      <c r="D3" s="228"/>
-      <c r="E3" s="214"/>
+      <c r="C3" s="254"/>
+      <c r="D3" s="254"/>
+      <c r="E3" s="213"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:9" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="212"/>
-      <c r="B4" s="229"/>
-      <c r="C4" s="229"/>
-      <c r="D4" s="229"/>
-      <c r="E4" s="214"/>
+      <c r="A4" s="211"/>
+      <c r="B4" s="255"/>
+      <c r="C4" s="255"/>
+      <c r="D4" s="255"/>
+      <c r="E4" s="213"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="215" t="s">
+      <c r="A5" s="214" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -2354,36 +2389,36 @@
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="216"/>
+      <c r="E5" s="215"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="217" t="s">
+      <c r="A6" s="216" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="218"/>
-      <c r="D6" s="218" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="219"/>
+      <c r="E6" s="218"/>
       <c r="F6" s="1"/>
       <c r="G6" s="136"/>
       <c r="H6" s="136"/>
       <c r="I6" s="137"/>
     </row>
     <row r="7" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="240" t="s">
+      <c r="A7" s="264" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="241"/>
-      <c r="C7" s="241"/>
-      <c r="D7" s="241"/>
-      <c r="E7" s="242"/>
+      <c r="B7" s="265"/>
+      <c r="C7" s="265"/>
+      <c r="D7" s="265"/>
+      <c r="E7" s="266"/>
       <c r="F7" s="5"/>
       <c r="G7" s="138"/>
       <c r="H7" s="138"/>
@@ -2396,10 +2431,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
-      <c r="B9" s="233" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="234"/>
+      <c r="B9" s="261" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="245"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -2408,8 +2443,8 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
-      <c r="B10" s="234"/>
-      <c r="C10" s="234"/>
+      <c r="B10" s="245"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -2418,8 +2453,8 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="234"/>
-      <c r="C11" s="234"/>
+      <c r="B11" s="245"/>
+      <c r="C11" s="245"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -2438,43 +2473,43 @@
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="243" t="s">
+      <c r="A14" s="267" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="234"/>
-      <c r="C14" s="234"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="234"/>
+      <c r="B14" s="245"/>
+      <c r="C14" s="245"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="234"/>
-      <c r="B15" s="234"/>
-      <c r="C15" s="234"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="234"/>
+      <c r="A15" s="245"/>
+      <c r="B15" s="245"/>
+      <c r="C15" s="245"/>
+      <c r="D15" s="245"/>
+      <c r="E15" s="245"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="234"/>
-      <c r="B16" s="234"/>
-      <c r="C16" s="234"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="234"/>
+      <c r="A16" s="245"/>
+      <c r="B16" s="245"/>
+      <c r="C16" s="245"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="234"/>
-      <c r="B17" s="234"/>
-      <c r="C17" s="234"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="234"/>
+      <c r="A17" s="245"/>
+      <c r="B17" s="245"/>
+      <c r="C17" s="245"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
     </row>
     <row r="18" spans="1:26" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
@@ -2517,12 +2552,12 @@
     </row>
     <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
-      <c r="D23" s="160">
-        <v>613132.9</v>
+      <c r="D23" s="159">
+        <v>715270.15</v>
       </c>
       <c r="E23" s="13"/>
     </row>
@@ -2530,7 +2565,7 @@
       <c r="A24" s="13"/>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
-      <c r="D24" s="160"/>
+      <c r="D24" s="159"/>
       <c r="E24" s="13"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -2558,7 +2593,7 @@
       <c r="A25" s="13"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
-      <c r="D25" s="160"/>
+      <c r="D25" s="159"/>
       <c r="E25" s="13"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -2588,8 +2623,8 @@
       </c>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
-      <c r="D26" s="160">
-        <v>-151750.41</v>
+      <c r="D26" s="159">
+        <v>-177029.35</v>
       </c>
       <c r="E26" s="13"/>
     </row>
@@ -2599,8 +2634,8 @@
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
-      <c r="D27" s="160">
-        <v>0.51</v>
+      <c r="D27" s="159">
+        <v>0.2</v>
       </c>
       <c r="E27" s="13"/>
       <c r="F27" s="1"/>
@@ -2631,9 +2666,9 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="161">
+      <c r="D28" s="160">
         <f>SUM(D23:D27)</f>
-        <v>461383</v>
+        <v>538241</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="1"/>
@@ -2660,18 +2695,18 @@
     </row>
     <row r="29" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
-      <c r="D29" s="160"/>
+      <c r="D29" s="159"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" spans="1:26" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
-      <c r="D30" s="160"/>
+      <c r="D30" s="159"/>
       <c r="E30" s="13"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -2699,14 +2734,14 @@
       <c r="A31" s="13"/>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
-      <c r="D31" s="160"/>
+      <c r="D31" s="159"/>
       <c r="E31" s="13"/>
     </row>
     <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
-      <c r="D32" s="162"/>
+      <c r="D32" s="161"/>
       <c r="E32" s="13"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -2734,7 +2769,7 @@
       <c r="A33" s="13"/>
       <c r="B33" s="13"/>
       <c r="C33" s="13"/>
-      <c r="D33" s="162"/>
+      <c r="D33" s="161"/>
       <c r="E33" s="13"/>
       <c r="F33" s="1"/>
     </row>
@@ -2744,7 +2779,7 @@
       </c>
       <c r="B34" s="13"/>
       <c r="C34" s="13"/>
-      <c r="D34" s="162"/>
+      <c r="D34" s="161"/>
       <c r="E34" s="13"/>
       <c r="F34" s="1"/>
     </row>
@@ -2754,7 +2789,7 @@
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
-      <c r="D35" s="162"/>
+      <c r="D35" s="161"/>
       <c r="E35" s="13"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -2782,7 +2817,7 @@
       <c r="A36" s="13"/>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
-      <c r="D36" s="162"/>
+      <c r="D36" s="161"/>
       <c r="E36" s="13"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2812,7 +2847,7 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
-      <c r="D37" s="163">
+      <c r="D37" s="162">
         <f>SUM(D29:D36)</f>
         <v>0</v>
       </c>
@@ -2845,10 +2880,10 @@
       </c>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
-      <c r="D38" s="164"/>
+      <c r="D38" s="163"/>
       <c r="E38" s="18">
         <f>D28+D37</f>
-        <v>461383</v>
+        <v>538241</v>
       </c>
       <c r="F38" s="19"/>
     </row>
@@ -2858,7 +2893,7 @@
       </c>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
-      <c r="D39" s="165"/>
+      <c r="D39" s="164"/>
       <c r="E39" s="20"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2886,11 +2921,11 @@
       <c r="A40" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="185" t="s">
-        <v>168</v>
+      <c r="B40" s="184" t="s">
+        <v>170</v>
       </c>
       <c r="C40" s="13"/>
-      <c r="D40" s="282">
+      <c r="D40" s="236">
         <v>30000</v>
       </c>
       <c r="E40" s="22"/>
@@ -2917,14 +2952,14 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="220" t="s">
+      <c r="A41" s="219" t="s">
         <v>18</v>
       </c>
-      <c r="B41" s="185" t="s">
-        <v>168</v>
+      <c r="B41" s="184" t="s">
+        <v>170</v>
       </c>
       <c r="C41" s="13"/>
-      <c r="D41" s="160">
+      <c r="D41" s="159">
         <v>125300</v>
       </c>
       <c r="E41" s="22"/>
@@ -2958,7 +2993,7 @@
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
-      <c r="D42" s="166"/>
+      <c r="D42" s="165"/>
       <c r="E42" s="23">
         <f>SUM(D40:D41)</f>
         <v>155300</v>
@@ -2991,21 +3026,21 @@
       </c>
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
-      <c r="D43" s="167"/>
+      <c r="D43" s="166"/>
       <c r="E43" s="24"/>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="239" t="s">
+      <c r="A44" s="262" t="s">
         <v>21</v>
       </c>
-      <c r="B44" s="225"/>
+      <c r="B44" s="249"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="169">
+      <c r="D44" s="168">
         <v>56041.08</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F44" s="1"/>
     </row>
@@ -3015,7 +3050,7 @@
       </c>
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
-      <c r="D45" s="166"/>
+      <c r="D45" s="165"/>
       <c r="E45" s="28">
         <f>SUM(D44:D44)</f>
         <v>56041.08</v>
@@ -3028,7 +3063,7 @@
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
-      <c r="D46" s="170"/>
+      <c r="D46" s="169"/>
       <c r="E46" s="30"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3056,7 +3091,7 @@
       <c r="A47" s="13"/>
       <c r="B47" s="13"/>
       <c r="C47" s="31"/>
-      <c r="D47" s="171"/>
+      <c r="D47" s="170"/>
       <c r="E47" s="33"/>
       <c r="F47" s="1"/>
     </row>
@@ -3066,27 +3101,27 @@
       </c>
       <c r="B48" s="13"/>
       <c r="C48" s="31"/>
-      <c r="D48" s="283">
-        <v>396693.7</v>
-      </c>
-      <c r="E48" s="146" t="s">
-        <v>173</v>
+      <c r="D48" s="237">
+        <v>341902.32</v>
+      </c>
+      <c r="E48" s="145" t="s">
+        <v>188</v>
       </c>
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C49" s="13"/>
-      <c r="D49" s="171">
-        <v>32007.51</v>
+      <c r="D49" s="170">
+        <v>27590.98</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -3113,18 +3148,18 @@
     <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="str">
         <f>A49</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>26</v>
       </c>
       <c r="C50" s="13"/>
-      <c r="D50" s="169">
-        <v>70861.06</v>
+      <c r="D50" s="168">
+        <v>64825.65</v>
       </c>
       <c r="E50" s="34" t="str">
         <f>E49</f>
-        <v>Debito 12/08</v>
+        <v>Debito 12/09</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -3133,18 +3168,18 @@
     <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="141" t="str">
         <f>A50</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B51" s="141" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="141"/>
-      <c r="D51" s="284">
-        <v>3556.39</v>
+      <c r="D51" s="238">
+        <v>3065.66</v>
       </c>
       <c r="E51" s="35" t="str">
         <f>E50</f>
-        <v>Debito 12/08</v>
+        <v>Debito 12/09</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -3156,10 +3191,10 @@
       </c>
       <c r="B52" s="143"/>
       <c r="C52" s="143"/>
-      <c r="D52" s="172"/>
+      <c r="D52" s="171"/>
       <c r="E52" s="28">
         <f>SUM(D47:D51)</f>
-        <v>503118.66000000003</v>
+        <v>437384.61</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -3171,7 +3206,7 @@
       </c>
       <c r="B53" s="29"/>
       <c r="C53" s="29"/>
-      <c r="D53" s="170"/>
+      <c r="D53" s="169"/>
       <c r="E53" s="30"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -3195,17 +3230,17 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="259" t="s">
-        <v>170</v>
-      </c>
-      <c r="B54" s="260"/>
+    <row r="54" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="250" t="s">
+        <v>172</v>
+      </c>
+      <c r="B54" s="263"/>
       <c r="C54" s="13"/>
-      <c r="D54" s="201">
+      <c r="D54" s="200">
         <v>108000</v>
       </c>
-      <c r="E54" s="146" t="s">
-        <v>173</v>
+      <c r="E54" s="34" t="s">
+        <v>187</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -3229,181 +3264,185 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="153" t="s">
+    <row r="55" spans="1:26" s="137" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="250" t="s">
+        <v>186</v>
+      </c>
+      <c r="B55" s="263"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="200">
+        <v>132289.29999999999</v>
+      </c>
+      <c r="E55" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" s="136"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="136"/>
+      <c r="J55" s="136"/>
+      <c r="K55" s="136"/>
+      <c r="L55" s="136"/>
+      <c r="M55" s="136"/>
+      <c r="N55" s="136"/>
+      <c r="O55" s="136"/>
+      <c r="P55" s="136"/>
+      <c r="Q55" s="136"/>
+      <c r="R55" s="136"/>
+      <c r="S55" s="136"/>
+      <c r="T55" s="136"/>
+      <c r="U55" s="136"/>
+      <c r="V55" s="136"/>
+      <c r="W55" s="136"/>
+      <c r="X55" s="136"/>
+      <c r="Y55" s="136"/>
+      <c r="Z55" s="136"/>
+    </row>
+    <row r="56" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="152" t="s">
         <v>30</v>
       </c>
-      <c r="B55" s="154"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="201">
-        <v>35000</v>
-      </c>
-      <c r="E55" s="146" t="s">
-        <v>173</v>
-      </c>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1"/>
-      <c r="W55" s="1"/>
-      <c r="X55" s="1"/>
-      <c r="Y55" s="1"/>
-      <c r="Z55" s="1"/>
-    </row>
-    <row r="56" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="124" t="s">
+      <c r="B56" s="153"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="200">
+        <v>40000</v>
+      </c>
+      <c r="E56" s="220" t="s">
+        <v>179</v>
+      </c>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1"/>
+      <c r="W56" s="1"/>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+    </row>
+    <row r="57" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="B56" s="123"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="285">
-        <v>31279.279999999999</v>
-      </c>
-      <c r="E56" s="144" t="s">
-        <v>178</v>
-      </c>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-    </row>
-    <row r="57" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="261" t="s">
-        <v>180</v>
-      </c>
-      <c r="B57" s="262"/>
-      <c r="C57" s="263"/>
-      <c r="D57" s="264">
-        <v>530000</v>
-      </c>
-      <c r="E57" s="133" t="s">
-        <v>181</v>
+      <c r="B57" s="123"/>
+      <c r="C57" s="37"/>
+      <c r="D57" s="239">
+        <v>32024.25</v>
+      </c>
+      <c r="E57" s="144" t="s">
+        <v>175</v>
       </c>
       <c r="F57" s="38"/>
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
     </row>
-    <row r="58" spans="1:26" s="137" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="224" t="s">
-        <v>175</v>
-      </c>
-      <c r="B58" s="225"/>
+    <row r="58" spans="1:26" s="137" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="256" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" s="257"/>
       <c r="C58" s="37"/>
-      <c r="D58" s="264">
-        <v>350000</v>
-      </c>
-      <c r="E58" s="221" t="s">
+      <c r="D58" s="239">
+        <v>300000</v>
+      </c>
+      <c r="E58" s="133" t="s">
+        <v>183</v>
+      </c>
+      <c r="F58" s="189"/>
+      <c r="G58" s="189"/>
+      <c r="H58" s="189"/>
+    </row>
+    <row r="59" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="256" t="s">
+        <v>181</v>
+      </c>
+      <c r="B59" s="257"/>
+      <c r="C59" s="221"/>
+      <c r="D59" s="222">
+        <v>450000</v>
+      </c>
+      <c r="E59" s="133" t="s">
+        <v>180</v>
+      </c>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38"/>
+      <c r="H59" s="38"/>
+    </row>
+    <row r="60" spans="1:26" s="137" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="242" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="243"/>
+      <c r="C60" s="221"/>
+      <c r="D60" s="222">
+        <v>336000</v>
+      </c>
+      <c r="E60" s="133" t="s">
+        <v>193</v>
+      </c>
+      <c r="F60" s="189"/>
+      <c r="G60" s="189"/>
+      <c r="H60" s="189"/>
+    </row>
+    <row r="61" spans="1:26" s="137" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="241" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" s="240"/>
+      <c r="C61" s="221"/>
+      <c r="D61" s="222">
+        <v>40000</v>
+      </c>
+      <c r="E61" s="133" t="s">
+        <v>194</v>
+      </c>
+      <c r="F61" s="189"/>
+      <c r="G61" s="189"/>
+      <c r="H61" s="189"/>
+    </row>
+    <row r="62" spans="1:26" s="137" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="250" t="s">
+        <v>178</v>
+      </c>
+      <c r="B62" s="249"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="222">
+        <v>20000</v>
+      </c>
+      <c r="E62" s="220" t="s">
+        <v>179</v>
+      </c>
+      <c r="F62" s="189"/>
+      <c r="G62" s="189"/>
+      <c r="H62" s="189"/>
+    </row>
+    <row r="63" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="250" t="s">
         <v>173</v>
       </c>
-      <c r="F58" s="190"/>
-      <c r="G58" s="190"/>
-      <c r="H58" s="190"/>
-    </row>
-    <row r="59" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="224" t="s">
-        <v>171</v>
-      </c>
-      <c r="B59" s="225"/>
-      <c r="C59" s="21"/>
-      <c r="D59" s="168">
-        <v>16994.62</v>
-      </c>
-      <c r="E59" s="133" t="s">
-        <v>177</v>
-      </c>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1"/>
-      <c r="W59" s="1"/>
-      <c r="X59" s="1"/>
-      <c r="Y59" s="1"/>
-      <c r="Z59" s="1"/>
-    </row>
-    <row r="60" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="224" t="s">
-        <v>182</v>
-      </c>
-      <c r="B60" s="225"/>
-      <c r="C60" s="21"/>
-      <c r="D60" s="168"/>
-      <c r="E60" s="145"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-    </row>
-    <row r="61" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="169"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="238"/>
-      <c r="B62" s="225"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="169"/>
-      <c r="E62" s="36"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-      <c r="Z62" s="1"/>
-    </row>
-    <row r="63" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="39"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="169"/>
-      <c r="E63" s="40"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
+      <c r="B63" s="249"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="167">
+        <v>16994.66</v>
+      </c>
+      <c r="E63" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -3423,68 +3462,38 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="224"/>
-      <c r="B64" s="230"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="236"/>
-      <c r="E64" s="222"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1"/>
-      <c r="W64" s="1"/>
-      <c r="X64" s="1"/>
-      <c r="Y64" s="1"/>
-      <c r="Z64" s="1"/>
-    </row>
-    <row r="65" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="231"/>
-      <c r="B65" s="232"/>
-      <c r="C65" s="41"/>
-      <c r="D65" s="237"/>
-      <c r="E65" s="223"/>
+    <row r="64" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="250" t="s">
+        <v>177</v>
+      </c>
+      <c r="B64" s="249"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="167">
+        <v>17256.25</v>
+      </c>
+      <c r="E64" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+    </row>
+    <row r="65" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="168"/>
+      <c r="E65" s="36"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1"/>
-      <c r="W65" s="1"/>
-      <c r="X65" s="1"/>
-      <c r="Y65" s="1"/>
-      <c r="Z65" s="1"/>
-    </row>
-    <row r="66" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="224"/>
-      <c r="B66" s="225"/>
+    </row>
+    <row r="66" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="248"/>
+      <c r="B66" s="249"/>
       <c r="C66" s="13"/>
-      <c r="D66" s="173"/>
-      <c r="E66" s="42"/>
+      <c r="D66" s="168"/>
+      <c r="E66" s="36"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
@@ -3507,12 +3516,12 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="224"/>
-      <c r="B67" s="225"/>
+    <row r="67" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="13"/>
+      <c r="B67" s="39"/>
       <c r="C67" s="13"/>
-      <c r="D67" s="173"/>
-      <c r="E67" s="42"/>
+      <c r="D67" s="168"/>
+      <c r="E67" s="40"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
@@ -3535,19 +3544,40 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="224"/>
-      <c r="B68" s="225"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="173"/>
-      <c r="E68" s="36"/>
-    </row>
-    <row r="69" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="173"/>
-      <c r="E69" s="36"/>
+    <row r="68" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="250"/>
+      <c r="B68" s="258"/>
+      <c r="C68" s="41"/>
+      <c r="D68" s="246"/>
+      <c r="E68" s="268"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+      <c r="M68" s="1"/>
+      <c r="N68" s="1"/>
+      <c r="O68" s="1"/>
+      <c r="P68" s="1"/>
+      <c r="Q68" s="1"/>
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1"/>
+      <c r="W68" s="1"/>
+      <c r="X68" s="1"/>
+      <c r="Y68" s="1"/>
+      <c r="Z68" s="1"/>
+    </row>
+    <row r="69" spans="1:26" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="259"/>
+      <c r="B69" s="260"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="247"/>
+      <c r="E69" s="269"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -3570,12 +3600,12 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="224"/>
-      <c r="B70" s="225"/>
+    <row r="70" spans="1:26" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="250"/>
+      <c r="B70" s="249"/>
       <c r="C70" s="13"/>
-      <c r="D70" s="173"/>
-      <c r="E70" s="36"/>
+      <c r="D70" s="172"/>
+      <c r="E70" s="42"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -3598,12 +3628,12 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="39"/>
-      <c r="B71" s="44"/>
+    <row r="71" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="250"/>
+      <c r="B71" s="249"/>
       <c r="C71" s="13"/>
-      <c r="D71" s="173"/>
-      <c r="E71" s="36"/>
+      <c r="D71" s="172"/>
+      <c r="E71" s="42"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -3627,39 +3657,18 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="224"/>
-      <c r="B72" s="225"/>
+      <c r="A72" s="250"/>
+      <c r="B72" s="249"/>
       <c r="C72" s="13"/>
-      <c r="D72" s="173"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="1"/>
-      <c r="X72" s="1"/>
-      <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
-    </row>
-    <row r="73" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="224"/>
-      <c r="B73" s="225"/>
+      <c r="D72" s="172"/>
+      <c r="E72" s="36"/>
+    </row>
+    <row r="73" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="13"/>
+      <c r="B73" s="43"/>
       <c r="C73" s="13"/>
-      <c r="D73" s="173"/>
-      <c r="E73" s="45"/>
+      <c r="D73" s="172"/>
+      <c r="E73" s="36"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
@@ -3682,12 +3691,12 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="226"/>
-      <c r="B74" s="225"/>
-      <c r="C74" s="46"/>
-      <c r="D74" s="173"/>
-      <c r="E74" s="45"/>
+    <row r="74" spans="1:26" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="250"/>
+      <c r="B74" s="249"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="172"/>
+      <c r="E74" s="36"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
@@ -3710,362 +3719,351 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
-      <c r="D75" s="166"/>
-      <c r="E75" s="28">
-        <f>SUM(D54:D60)</f>
-        <v>1071273.9000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="166"/>
-      <c r="E76" s="47"/>
-    </row>
-    <row r="77" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B77" s="13"/>
+    <row r="75" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="39"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="13"/>
+      <c r="D75" s="172"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
+      <c r="P75" s="1"/>
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+    </row>
+    <row r="76" spans="1:26" ht="33.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="250"/>
+      <c r="B76" s="249"/>
+      <c r="C76" s="13"/>
+      <c r="D76" s="172"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
+      <c r="L76" s="1"/>
+      <c r="M76" s="1"/>
+      <c r="N76" s="1"/>
+      <c r="O76" s="1"/>
+      <c r="P76" s="1"/>
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+    </row>
+    <row r="77" spans="1:26" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="250"/>
+      <c r="B77" s="249"/>
       <c r="C77" s="13"/>
-      <c r="D77" s="171">
-        <v>35450</v>
-      </c>
-      <c r="E77" s="146" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="171"/>
-      <c r="E78" s="49"/>
+      <c r="D77" s="172"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+    </row>
+    <row r="78" spans="1:26" ht="36.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="251"/>
+      <c r="B78" s="249"/>
+      <c r="C78" s="46"/>
+      <c r="D78" s="172"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+      <c r="K78" s="1"/>
+      <c r="L78" s="1"/>
+      <c r="M78" s="1"/>
+      <c r="N78" s="1"/>
+      <c r="O78" s="1"/>
+      <c r="P78" s="1"/>
+      <c r="Q78" s="1"/>
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="174"/>
-      <c r="E79" s="50">
-        <f>SUM(D77:D78)</f>
-        <v>35450</v>
-      </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1"/>
-      <c r="W79" s="1"/>
-      <c r="X79" s="1"/>
-      <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="165"/>
+      <c r="E79" s="28">
+        <f>SUM(D54:D64)</f>
+        <v>1492564.46</v>
+      </c>
     </row>
     <row r="80" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B80" s="51"/>
+        <v>33</v>
+      </c>
+      <c r="B80" s="17"/>
       <c r="C80" s="17"/>
-      <c r="D80" s="164"/>
-      <c r="E80" s="47">
+      <c r="D80" s="165"/>
+      <c r="E80" s="47"/>
+    </row>
+    <row r="81" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="B81" s="13"/>
+      <c r="C81" s="13"/>
+      <c r="D81" s="170">
+        <v>13500</v>
+      </c>
+      <c r="E81" s="145"/>
+    </row>
+    <row r="82" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="170"/>
+      <c r="E82" s="49"/>
+    </row>
+    <row r="83" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="173"/>
+      <c r="E83" s="50">
+        <f>SUM(D81:D82)</f>
+        <v>13500</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
+      <c r="K83" s="1"/>
+      <c r="L83" s="1"/>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
+      <c r="P83" s="1"/>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+    </row>
+    <row r="84" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="51"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="163"/>
+      <c r="E84" s="47">
         <f>850.17+698.43+4797.54+618.63+2.1+2364+10+1202.53+1583.5+3434+961.5+2275.93+1316.37+1224+2364.03+534+4200+154.8+1600+1200+2351.5+457.76+2442+6000</f>
         <v>42642.79</v>
       </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
-      <c r="U80" s="1"/>
-      <c r="V80" s="1"/>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
-      <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
-    </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
+      <c r="K84" s="1"/>
+      <c r="L84" s="1"/>
+      <c r="M84" s="1"/>
+      <c r="N84" s="1"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="1"/>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+    </row>
+    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="202">
-        <v>49507.040000000001</v>
-      </c>
-      <c r="E81" s="52"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="1"/>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="1"/>
-      <c r="V81" s="1"/>
-      <c r="W81" s="1"/>
-      <c r="X81" s="1"/>
-      <c r="Y81" s="1"/>
-      <c r="Z81" s="1"/>
-    </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
+      <c r="B85" s="13"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="201">
+        <v>53643.55</v>
+      </c>
+      <c r="E85" s="52"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
+      <c r="K85" s="1"/>
+      <c r="L85" s="1"/>
+      <c r="M85" s="1"/>
+      <c r="N85" s="1"/>
+      <c r="O85" s="1"/>
+      <c r="P85" s="1"/>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+    </row>
+    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="169">
-        <v>30000</v>
-      </c>
-      <c r="E82" s="42"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
-      <c r="U82" s="1"/>
-      <c r="V82" s="1"/>
-      <c r="W82" s="1"/>
-      <c r="X82" s="1"/>
-      <c r="Y82" s="1"/>
-      <c r="Z82" s="1"/>
-    </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="53" t="s">
+      <c r="B86" s="13"/>
+      <c r="C86" s="13"/>
+      <c r="D86" s="168">
+        <v>41000</v>
+      </c>
+      <c r="E86" s="42"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
+      <c r="K86" s="1"/>
+      <c r="L86" s="1"/>
+      <c r="M86" s="1"/>
+      <c r="N86" s="1"/>
+      <c r="O86" s="1"/>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+    </row>
+    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="53"/>
-      <c r="C83" s="53"/>
-      <c r="D83" s="140"/>
-      <c r="E83" s="28">
-        <f>SUM(D81:D82)</f>
-        <v>79507.040000000008</v>
-      </c>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="54"/>
-      <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="55" t="s">
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="140"/>
+      <c r="E87" s="28">
+        <f>SUM(D85:D86)</f>
+        <v>94643.55</v>
+      </c>
+      <c r="F87" s="1"/>
+    </row>
+    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="13"/>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="13"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="1"/>
+    </row>
+    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="B85" s="55"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="57">
+      <c r="B89" s="55"/>
+      <c r="C89" s="55"/>
+      <c r="D89" s="56"/>
+      <c r="E89" s="57">
         <f>595283.53</f>
         <v>595283.53</v>
       </c>
-      <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="58"/>
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="60"/>
-    </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="61" t="s">
+      <c r="F89" s="1"/>
+    </row>
+    <row r="90" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="58"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="60"/>
+    </row>
+    <row r="91" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B87" s="62"/>
-      <c r="C87" s="63"/>
-      <c r="D87" s="63"/>
-      <c r="E87" s="64">
-        <f>(SUM(E31:E85))</f>
-        <v>3000000</v>
-      </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="188"/>
-      <c r="H87" s="206"/>
-    </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="1"/>
-      <c r="M89" s="1"/>
-      <c r="N89" s="1"/>
-      <c r="O89" s="1"/>
-      <c r="P89" s="1"/>
-      <c r="Q89" s="1"/>
-      <c r="R89" s="1"/>
-      <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
-      <c r="U89" s="1"/>
-      <c r="V89" s="1"/>
-      <c r="W89" s="1"/>
-      <c r="X89" s="1"/>
-      <c r="Y89" s="1"/>
-      <c r="Z89" s="1"/>
-    </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="10"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="1"/>
-      <c r="M90" s="1"/>
-      <c r="N90" s="1"/>
-      <c r="O90" s="1"/>
-      <c r="P90" s="1"/>
-      <c r="Q90" s="1"/>
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="1"/>
-      <c r="V90" s="1"/>
-      <c r="W90" s="1"/>
-      <c r="X90" s="1"/>
-      <c r="Y90" s="1"/>
-      <c r="Z90" s="1"/>
-    </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="135"/>
-      <c r="B91" s="135"/>
-      <c r="C91" s="134"/>
-      <c r="D91" s="32"/>
-      <c r="E91" s="48"/>
+      <c r="B91" s="62"/>
+      <c r="C91" s="63"/>
+      <c r="D91" s="63"/>
+      <c r="E91" s="64">
+        <f>(SUM(E31:E89))</f>
+        <v>3425601.0199999996</v>
+      </c>
       <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-      <c r="N91" s="1"/>
-      <c r="O91" s="1"/>
-      <c r="P91" s="1"/>
-      <c r="Q91" s="1"/>
-      <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
-      <c r="U91" s="1"/>
-      <c r="V91" s="1"/>
-      <c r="W91" s="1"/>
-      <c r="X91" s="1"/>
-      <c r="Y91" s="1"/>
-      <c r="Z91" s="1"/>
-    </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="135"/>
-      <c r="B92" s="135"/>
-      <c r="C92" s="134"/>
-      <c r="D92" s="32">
-        <v>0</v>
-      </c>
-      <c r="E92" s="32"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="1"/>
-      <c r="M92" s="1"/>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="1"/>
-      <c r="V92" s="1"/>
-      <c r="W92" s="1"/>
-      <c r="X92" s="1"/>
-      <c r="Y92" s="1"/>
-      <c r="Z92" s="1"/>
-    </row>
+      <c r="G91" s="187"/>
+      <c r="H91" s="205"/>
+    </row>
+    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B93" s="66"/>
-      <c r="C93" s="66"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67">
-        <f>SUM(D91:D92)</f>
-        <v>0</v>
-      </c>
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1"/>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -4088,12 +4086,14 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
+    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" s="8"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="11"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
@@ -4116,12 +4116,12 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="135"/>
+      <c r="B95" s="135"/>
+      <c r="C95" s="134"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="48"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
@@ -4145,13 +4145,13 @@
       <c r="Z95" s="1"/>
     </row>
     <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="203" t="s">
-        <v>39</v>
-      </c>
-      <c r="B96" s="203"/>
-      <c r="C96" s="203"/>
-      <c r="D96" s="203"/>
-      <c r="E96" s="204"/>
+      <c r="A96" s="135"/>
+      <c r="B96" s="135"/>
+      <c r="C96" s="134"/>
+      <c r="D96" s="32">
+        <v>0</v>
+      </c>
+      <c r="E96" s="32"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -4174,12 +4174,17 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="B97" s="66"/>
+      <c r="C97" s="66"/>
+      <c r="D97" s="67"/>
+      <c r="E97" s="67">
+        <f>SUM(D95:D96)</f>
+        <v>0</v>
+      </c>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
       <c r="H97" s="1"/>
@@ -4202,17 +4207,12 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="B98" s="62"/>
-      <c r="C98" s="63"/>
-      <c r="D98" s="63"/>
-      <c r="E98" s="64">
-        <f>E93+E96</f>
-        <v>0</v>
-      </c>
+    <row r="98" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
       <c r="H98" s="1"/>
@@ -4235,7 +4235,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4264,16 +4264,13 @@
       <c r="Z99" s="1"/>
     </row>
     <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="68" t="s">
-        <v>41</v>
-      </c>
-      <c r="B100" s="69">
-        <f>E87</f>
-        <v>3000000</v>
-      </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
+      <c r="A100" s="202" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" s="202"/>
+      <c r="C100" s="202"/>
+      <c r="D100" s="202"/>
+      <c r="E100" s="203"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
       <c r="H100" s="1"/>
@@ -4296,26 +4293,45 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="68" t="s">
-        <v>42</v>
-      </c>
-      <c r="B101" s="69">
-        <f>E87-E85</f>
-        <v>2404716.4699999997</v>
-      </c>
+    <row r="101" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="1"/>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+      <c r="K101" s="1"/>
+      <c r="L101" s="1"/>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="1"/>
+      <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
+      <c r="Z101" s="1"/>
     </row>
     <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="68" t="s">
-        <v>43</v>
-      </c>
-      <c r="B102" s="69">
-        <f>E98-E96</f>
+      <c r="A102" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" s="62"/>
+      <c r="C102" s="63"/>
+      <c r="D102" s="63"/>
+      <c r="E102" s="64">
+        <f>E97+E100</f>
         <v>0</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -4339,13 +4355,8 @@
       <c r="Z102" s="1"/>
     </row>
     <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="B103" s="69">
-        <f>E98</f>
-        <v>0</v>
-      </c>
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -4372,34 +4383,112 @@
       <c r="Z103" s="1"/>
     </row>
     <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
+      <c r="A104" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="B104" s="69">
+        <f>E91</f>
+        <v>3425601.0199999996</v>
+      </c>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-    </row>
-    <row r="105" spans="1:26" s="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="277"/>
-      <c r="B105" s="277"/>
-      <c r="C105" s="277"/>
-      <c r="D105" s="277"/>
-      <c r="E105" s="277"/>
-    </row>
-    <row r="106" spans="1:26" s="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="279" t="s">
-        <v>183</v>
-      </c>
-      <c r="B106" s="279"/>
-      <c r="C106" s="277"/>
-      <c r="D106" s="277"/>
-      <c r="E106" s="277"/>
-    </row>
-    <row r="107" spans="1:26" s="278" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="279"/>
-      <c r="B107" s="279"/>
-      <c r="C107" s="277"/>
-      <c r="D107" s="277"/>
-      <c r="E107" s="277"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1"/>
+      <c r="V104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
+      <c r="Z104" s="1"/>
+    </row>
+    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" s="69">
+        <f>E91-E89</f>
+        <v>2830317.4899999993</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="B106" s="69">
+        <f>E102-E100</f>
+        <v>0</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1"/>
+      <c r="J106" s="1"/>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
+      <c r="Z106" s="1"/>
+    </row>
+    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="B107" s="69">
+        <f>E102</f>
+        <v>0</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1"/>
+      <c r="J107" s="1"/>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
+      <c r="V107" s="1"/>
+      <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
+      <c r="Z107" s="1"/>
     </row>
     <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
@@ -4408,455 +4497,497 @@
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
     </row>
-    <row r="109" spans="1:26" s="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="279" t="s">
-        <v>184</v>
-      </c>
-      <c r="B109" s="279"/>
-      <c r="C109" s="277"/>
-      <c r="D109" s="277"/>
-      <c r="E109" s="277"/>
-    </row>
-    <row r="110" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="279"/>
-      <c r="B110" s="279"/>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-    </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
+    <row r="109" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="136"/>
+      <c r="B109" s="136"/>
+      <c r="C109" s="136"/>
+      <c r="D109" s="136"/>
+      <c r="E109" s="136"/>
+    </row>
+    <row r="110" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="252" t="s">
+        <v>164</v>
+      </c>
+      <c r="B110" s="252"/>
+      <c r="C110" s="136"/>
+      <c r="D110" s="136"/>
+      <c r="E110" s="136"/>
+    </row>
+    <row r="111" spans="1:26" s="137" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="252"/>
+      <c r="B111" s="252"/>
+      <c r="C111" s="136"/>
+      <c r="D111" s="136"/>
+      <c r="E111" s="136"/>
     </row>
     <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="128" t="s">
+      <c r="A112" s="1"/>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+    </row>
+    <row r="113" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="252" t="s">
+        <v>165</v>
+      </c>
+      <c r="B113" s="252"/>
+      <c r="C113" s="136"/>
+      <c r="D113" s="136"/>
+      <c r="E113" s="136"/>
+    </row>
+    <row r="114" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="252"/>
+      <c r="B114" s="252"/>
+      <c r="C114" s="1"/>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+    </row>
+    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+    </row>
+    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="B112" s="129"/>
-      <c r="C112" s="70"/>
-    </row>
-    <row r="113" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="132" t="s">
+      <c r="B116" s="129"/>
+      <c r="C116" s="70"/>
+    </row>
+    <row r="117" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="B113" s="205">
-        <v>480739.1799999983</v>
-      </c>
-      <c r="C113" s="71"/>
-    </row>
-    <row r="114" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="130" t="s">
+      <c r="B117" s="204">
+        <v>1681142.8499999987</v>
+      </c>
+      <c r="C117" s="71"/>
+    </row>
+    <row r="118" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="130" t="s">
         <v>47</v>
       </c>
-      <c r="B114" s="131">
+      <c r="B118" s="131">
         <f>'Copia de PRORRATEO'!H37</f>
-        <v>3745120.1399999997</v>
-      </c>
-      <c r="C114" s="70"/>
-    </row>
-    <row r="115" spans="1:26" s="137" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="130" t="s">
+        <v>3430553.54</v>
+      </c>
+      <c r="C118" s="70"/>
+    </row>
+    <row r="119" spans="1:26" s="137" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="130" t="s">
         <v>161</v>
       </c>
-      <c r="B115" s="187"/>
-      <c r="C115" s="186"/>
-    </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="72" t="s">
+      <c r="B119" s="186">
+        <f>-2915-2789</f>
+        <v>-5704</v>
+      </c>
+      <c r="C119" s="185"/>
+    </row>
+    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="B116" s="73">
-        <f>B140</f>
+      <c r="B120" s="73">
+        <f>B146</f>
         <v>0</v>
       </c>
-      <c r="C116" s="70"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
-      <c r="J116" s="1"/>
-      <c r="K116" s="1"/>
-      <c r="L116" s="1"/>
-      <c r="M116" s="1"/>
-      <c r="N116" s="1"/>
-      <c r="O116" s="1"/>
-      <c r="P116" s="1"/>
-      <c r="Q116" s="1"/>
-      <c r="R116" s="1"/>
-      <c r="S116" s="1"/>
-      <c r="T116" s="1"/>
-      <c r="U116" s="1"/>
-      <c r="V116" s="1"/>
-      <c r="W116" s="1"/>
-      <c r="X116" s="1"/>
-      <c r="Y116" s="1"/>
-      <c r="Z116" s="1"/>
-    </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="74" t="s">
+      <c r="C120" s="70"/>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1"/>
+      <c r="N120" s="1"/>
+      <c r="O120" s="1"/>
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="U120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
+      <c r="Z120" s="1"/>
+    </row>
+    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="B117" s="73">
-        <f>-B101</f>
-        <v>-2404716.4699999997</v>
-      </c>
-      <c r="C117" s="70"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="1"/>
-      <c r="L117" s="1"/>
-      <c r="M117" s="1"/>
-      <c r="N117" s="1"/>
-      <c r="O117" s="1"/>
-      <c r="P117" s="1"/>
-      <c r="Q117" s="1"/>
-      <c r="R117" s="1"/>
-      <c r="S117" s="1"/>
-      <c r="T117" s="1"/>
-      <c r="U117" s="1"/>
-      <c r="V117" s="1"/>
-      <c r="W117" s="1"/>
-      <c r="X117" s="1"/>
-      <c r="Y117" s="1"/>
-      <c r="Z117" s="1"/>
-    </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="75" t="s">
+      <c r="B121" s="73">
+        <f>-B105</f>
+        <v>-2830317.4899999993</v>
+      </c>
+      <c r="C121" s="70"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+      <c r="N121" s="1"/>
+      <c r="O121" s="1"/>
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1"/>
+      <c r="T121" s="1"/>
+      <c r="U121" s="1"/>
+      <c r="V121" s="1"/>
+      <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
+      <c r="Z121" s="1"/>
+    </row>
+    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="B118" s="73">
-        <f>-(B102)</f>
+      <c r="B122" s="73">
+        <f>-(B106)</f>
         <v>0</v>
       </c>
-      <c r="C118" s="70"/>
-    </row>
-    <row r="119" spans="1:26" s="278" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="B119" s="281">
+      <c r="C122" s="70"/>
+    </row>
+    <row r="123" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B123" s="73">
+        <v>-91004</v>
+      </c>
+      <c r="C123" s="185"/>
+    </row>
+    <row r="124" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="B124" s="235">
         <v>90000</v>
       </c>
-      <c r="C119" s="280"/>
-    </row>
-    <row r="120" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="B120" s="73">
-        <v>-115000</v>
-      </c>
-      <c r="C120" s="70"/>
-    </row>
-    <row r="121" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="75" t="s">
-        <v>186</v>
-      </c>
-      <c r="B121" s="73">
-        <v>-115000</v>
-      </c>
-      <c r="C121" s="70"/>
-    </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="76" t="s">
+      <c r="C124" s="185"/>
+    </row>
+    <row r="125" spans="1:26" s="137" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="75" t="s">
+        <v>196</v>
+      </c>
+      <c r="B125" s="235">
+        <f>228000-132000</f>
+        <v>96000</v>
+      </c>
+      <c r="C125" s="185"/>
+    </row>
+    <row r="126" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="75" t="s">
+        <v>190</v>
+      </c>
+      <c r="B126" s="73">
+        <v>-26000</v>
+      </c>
+      <c r="C126" s="70"/>
+    </row>
+    <row r="127" spans="1:26" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="75"/>
+      <c r="B127" s="73"/>
+      <c r="C127" s="70"/>
+    </row>
+    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B122" s="77">
-        <f>SUM(B113:B121)</f>
-        <v>1681142.8499999987</v>
-      </c>
-      <c r="C122" s="78"/>
-    </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="1"/>
-      <c r="B123" s="60"/>
-      <c r="C123" s="78"/>
-      <c r="D123" s="60"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-      <c r="K123" s="1"/>
-      <c r="L123" s="1"/>
-      <c r="M123" s="1"/>
-      <c r="N123" s="1"/>
-      <c r="O123" s="1"/>
-      <c r="P123" s="1"/>
-      <c r="Q123" s="1"/>
-      <c r="R123" s="1"/>
-      <c r="S123" s="1"/>
-      <c r="T123" s="1"/>
-      <c r="U123" s="1"/>
-      <c r="V123" s="1"/>
-      <c r="W123" s="1"/>
-      <c r="X123" s="1"/>
-      <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
-    </row>
-    <row r="124" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="1"/>
-      <c r="B124" s="79"/>
-      <c r="C124" s="78"/>
-    </row>
-    <row r="125" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="60"/>
-      <c r="C125" s="80"/>
-      <c r="D125" s="27"/>
-      <c r="E125" s="27"/>
-      <c r="F125" s="27"/>
-      <c r="G125" s="27"/>
-      <c r="H125" s="27"/>
-      <c r="I125" s="27"/>
-      <c r="J125" s="27"/>
-      <c r="K125" s="27"/>
-      <c r="L125" s="27"/>
-      <c r="M125" s="27"/>
-      <c r="N125" s="27"/>
-      <c r="O125" s="27"/>
-      <c r="P125" s="27"/>
-      <c r="Q125" s="27"/>
-      <c r="R125" s="27"/>
-      <c r="S125" s="27"/>
-      <c r="T125" s="27"/>
-      <c r="U125" s="27"/>
-      <c r="V125" s="27"/>
-      <c r="W125" s="27"/>
-      <c r="X125" s="27"/>
-      <c r="Y125" s="27"/>
-      <c r="Z125" s="27"/>
-    </row>
-    <row r="126" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="81" t="s">
+      <c r="B128" s="77">
+        <f>SUM(B117:B127)</f>
+        <v>2344670.8999999994</v>
+      </c>
+      <c r="C128" s="78"/>
+    </row>
+    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1"/>
+      <c r="B129" s="60"/>
+      <c r="C129" s="78"/>
+      <c r="D129" s="60"/>
+      <c r="E129" s="1"/>
+      <c r="F129" s="1"/>
+      <c r="G129" s="1"/>
+      <c r="H129" s="1"/>
+      <c r="I129" s="1"/>
+      <c r="J129" s="1"/>
+      <c r="K129" s="1"/>
+      <c r="L129" s="1"/>
+      <c r="M129" s="1"/>
+      <c r="N129" s="1"/>
+      <c r="O129" s="1"/>
+      <c r="P129" s="1"/>
+      <c r="Q129" s="1"/>
+      <c r="R129" s="1"/>
+      <c r="S129" s="1"/>
+      <c r="T129" s="1"/>
+      <c r="U129" s="1"/>
+      <c r="V129" s="1"/>
+      <c r="W129" s="1"/>
+      <c r="X129" s="1"/>
+      <c r="Y129" s="1"/>
+      <c r="Z129" s="1"/>
+    </row>
+    <row r="130" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+      <c r="B130" s="79"/>
+      <c r="C130" s="78"/>
+    </row>
+    <row r="131" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B131" s="60"/>
+      <c r="C131" s="80"/>
+      <c r="D131" s="27"/>
+      <c r="E131" s="27"/>
+      <c r="F131" s="27"/>
+      <c r="G131" s="27"/>
+      <c r="H131" s="27"/>
+      <c r="I131" s="27"/>
+      <c r="J131" s="27"/>
+      <c r="K131" s="27"/>
+      <c r="L131" s="27"/>
+      <c r="M131" s="27"/>
+      <c r="N131" s="27"/>
+      <c r="O131" s="27"/>
+      <c r="P131" s="27"/>
+      <c r="Q131" s="27"/>
+      <c r="R131" s="27"/>
+      <c r="S131" s="27"/>
+      <c r="T131" s="27"/>
+      <c r="U131" s="27"/>
+      <c r="V131" s="27"/>
+      <c r="W131" s="27"/>
+      <c r="X131" s="27"/>
+      <c r="Y131" s="27"/>
+      <c r="Z131" s="27"/>
+    </row>
+    <row r="132" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="81" t="s">
         <v>51</v>
       </c>
-      <c r="B126" s="32"/>
-      <c r="C126" s="80"/>
-      <c r="D126" s="82"/>
-      <c r="E126" s="27"/>
-      <c r="F126" s="27"/>
-      <c r="G126" s="27"/>
-      <c r="H126" s="27"/>
-      <c r="I126" s="27"/>
-      <c r="J126" s="27"/>
-      <c r="K126" s="27"/>
-      <c r="L126" s="27"/>
-      <c r="M126" s="27"/>
-      <c r="N126" s="27"/>
-      <c r="O126" s="27"/>
-      <c r="P126" s="27"/>
-      <c r="Q126" s="27"/>
-      <c r="R126" s="27"/>
-      <c r="S126" s="27"/>
-      <c r="T126" s="27"/>
-      <c r="U126" s="27"/>
-      <c r="V126" s="27"/>
-      <c r="W126" s="27"/>
-      <c r="X126" s="27"/>
-      <c r="Y126" s="27"/>
-      <c r="Z126" s="27"/>
-    </row>
-    <row r="127" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="13" t="s">
+      <c r="B132" s="32"/>
+      <c r="C132" s="80"/>
+      <c r="D132" s="82"/>
+      <c r="E132" s="27"/>
+      <c r="F132" s="27"/>
+      <c r="G132" s="27"/>
+      <c r="H132" s="27"/>
+      <c r="I132" s="27"/>
+      <c r="J132" s="27"/>
+      <c r="K132" s="27"/>
+      <c r="L132" s="27"/>
+      <c r="M132" s="27"/>
+      <c r="N132" s="27"/>
+      <c r="O132" s="27"/>
+      <c r="P132" s="27"/>
+      <c r="Q132" s="27"/>
+      <c r="R132" s="27"/>
+      <c r="S132" s="27"/>
+      <c r="T132" s="27"/>
+      <c r="U132" s="27"/>
+      <c r="V132" s="27"/>
+      <c r="W132" s="27"/>
+      <c r="X132" s="27"/>
+      <c r="Y132" s="27"/>
+      <c r="Z132" s="27"/>
+    </row>
+    <row r="133" spans="1:26" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B127" s="32">
+      <c r="B133" s="32">
         <v>0</v>
       </c>
-      <c r="C127" s="80"/>
-      <c r="D127" s="27"/>
-      <c r="E127" s="27"/>
-      <c r="F127" s="27"/>
-      <c r="G127" s="27"/>
-      <c r="H127" s="27"/>
-      <c r="I127" s="27"/>
-      <c r="J127" s="27"/>
-      <c r="K127" s="27"/>
-      <c r="L127" s="27"/>
-      <c r="M127" s="27"/>
-      <c r="N127" s="27"/>
-      <c r="O127" s="27"/>
-      <c r="P127" s="27"/>
-      <c r="Q127" s="27"/>
-      <c r="R127" s="27"/>
-      <c r="S127" s="27"/>
-      <c r="T127" s="27"/>
-      <c r="U127" s="27"/>
-      <c r="V127" s="27"/>
-      <c r="W127" s="27"/>
-      <c r="X127" s="27"/>
-      <c r="Y127" s="27"/>
-      <c r="Z127" s="27"/>
-    </row>
-    <row r="128" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="13" t="s">
+      <c r="C133" s="80"/>
+      <c r="D133" s="27"/>
+      <c r="E133" s="27"/>
+      <c r="F133" s="27"/>
+      <c r="G133" s="27"/>
+      <c r="H133" s="27"/>
+      <c r="I133" s="27"/>
+      <c r="J133" s="27"/>
+      <c r="K133" s="27"/>
+      <c r="L133" s="27"/>
+      <c r="M133" s="27"/>
+      <c r="N133" s="27"/>
+      <c r="O133" s="27"/>
+      <c r="P133" s="27"/>
+      <c r="Q133" s="27"/>
+      <c r="R133" s="27"/>
+      <c r="S133" s="27"/>
+      <c r="T133" s="27"/>
+      <c r="U133" s="27"/>
+      <c r="V133" s="27"/>
+      <c r="W133" s="27"/>
+      <c r="X133" s="27"/>
+      <c r="Y133" s="27"/>
+      <c r="Z133" s="27"/>
+    </row>
+    <row r="134" spans="1:26" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B128" s="32">
+      <c r="B134" s="32">
         <v>0</v>
       </c>
-      <c r="C128" s="78"/>
-      <c r="D128" s="60"/>
-    </row>
-    <row r="129" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="13" t="s">
+      <c r="C134" s="78"/>
+      <c r="D134" s="60"/>
+    </row>
+    <row r="135" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B129" s="32">
+      <c r="B135" s="32">
         <v>0</v>
       </c>
-      <c r="C129" s="78"/>
-    </row>
-    <row r="130" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="13" t="s">
+      <c r="C135" s="78"/>
+    </row>
+    <row r="136" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B130" s="32">
+      <c r="B136" s="32">
         <v>0</v>
       </c>
-      <c r="C130" s="83"/>
-    </row>
-    <row r="131" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="81" t="s">
+      <c r="C136" s="83"/>
+    </row>
+    <row r="137" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="B131" s="84">
-        <f>SUM(B127:B130)</f>
+      <c r="B137" s="84">
+        <f>SUM(B133:B136)</f>
         <v>0</v>
       </c>
-      <c r="C131" s="70"/>
-    </row>
-    <row r="132" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="133" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="235" t="s">
+      <c r="C137" s="70"/>
+    </row>
+    <row r="138" spans="1:26" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" spans="1:26" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="244" t="s">
         <v>55</v>
       </c>
-      <c r="B134" s="234"/>
-      <c r="C134" s="234"/>
-    </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="234"/>
-      <c r="B135" s="234"/>
-      <c r="C135" s="234"/>
-    </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="13"/>
-      <c r="B136" s="157"/>
-      <c r="C136" s="32">
+      <c r="B140" s="245"/>
+      <c r="C140" s="245"/>
+    </row>
+    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="245"/>
+      <c r="B141" s="245"/>
+      <c r="C141" s="245"/>
+    </row>
+    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="13"/>
+      <c r="B142" s="156"/>
+      <c r="C142" s="32">
         <v>11948.17</v>
       </c>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="13"/>
-      <c r="B137" s="158"/>
-      <c r="C137" s="32">
+    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="13"/>
+      <c r="B143" s="157"/>
+      <c r="C143" s="32">
         <v>52000</v>
       </c>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="85"/>
-      <c r="B138" s="158"/>
-      <c r="C138" s="32">
+    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="85"/>
+      <c r="B144" s="157"/>
+      <c r="C144" s="32">
         <v>61209</v>
       </c>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
-      <c r="J138" s="1"/>
-      <c r="K138" s="1"/>
-      <c r="L138" s="1"/>
-      <c r="M138" s="1"/>
-      <c r="N138" s="1"/>
-      <c r="O138" s="1"/>
-      <c r="P138" s="1"/>
-      <c r="Q138" s="1"/>
-      <c r="R138" s="1"/>
-      <c r="S138" s="1"/>
-      <c r="T138" s="1"/>
-      <c r="U138" s="1"/>
-      <c r="V138" s="1"/>
-      <c r="W138" s="1"/>
-      <c r="X138" s="1"/>
-      <c r="Y138" s="1"/>
-      <c r="Z138" s="1"/>
-    </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="72"/>
-      <c r="B139" s="158"/>
-      <c r="C139" s="32">
+      <c r="D144" s="1"/>
+      <c r="E144" s="1"/>
+      <c r="F144" s="1"/>
+      <c r="G144" s="1"/>
+      <c r="H144" s="1"/>
+      <c r="I144" s="1"/>
+      <c r="J144" s="1"/>
+      <c r="K144" s="1"/>
+      <c r="L144" s="1"/>
+      <c r="M144" s="1"/>
+      <c r="N144" s="1"/>
+      <c r="O144" s="1"/>
+      <c r="P144" s="1"/>
+      <c r="Q144" s="1"/>
+      <c r="R144" s="1"/>
+      <c r="S144" s="1"/>
+      <c r="T144" s="1"/>
+      <c r="U144" s="1"/>
+      <c r="V144" s="1"/>
+      <c r="W144" s="1"/>
+      <c r="X144" s="1"/>
+      <c r="Y144" s="1"/>
+      <c r="Z144" s="1"/>
+    </row>
+    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="72"/>
+      <c r="B145" s="157"/>
+      <c r="C145" s="32">
         <v>40000</v>
       </c>
-      <c r="D139" s="1"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
-      <c r="J139" s="1"/>
-      <c r="K139" s="1"/>
-      <c r="L139" s="1"/>
-      <c r="M139" s="1"/>
-      <c r="N139" s="1"/>
-      <c r="O139" s="1"/>
-      <c r="P139" s="1"/>
-      <c r="Q139" s="1"/>
-      <c r="R139" s="1"/>
-      <c r="S139" s="1"/>
-      <c r="T139" s="1"/>
-      <c r="U139" s="1"/>
-      <c r="V139" s="1"/>
-      <c r="W139" s="1"/>
-      <c r="X139" s="1"/>
-      <c r="Y139" s="1"/>
-      <c r="Z139" s="1"/>
-    </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="86" t="s">
+      <c r="D145" s="1"/>
+      <c r="E145" s="1"/>
+      <c r="F145" s="1"/>
+      <c r="G145" s="1"/>
+      <c r="H145" s="1"/>
+      <c r="I145" s="1"/>
+      <c r="J145" s="1"/>
+      <c r="K145" s="1"/>
+      <c r="L145" s="1"/>
+      <c r="M145" s="1"/>
+      <c r="N145" s="1"/>
+      <c r="O145" s="1"/>
+      <c r="P145" s="1"/>
+      <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+      <c r="S145" s="1"/>
+      <c r="T145" s="1"/>
+      <c r="U145" s="1"/>
+      <c r="V145" s="1"/>
+      <c r="W145" s="1"/>
+      <c r="X145" s="1"/>
+      <c r="Y145" s="1"/>
+      <c r="Z145" s="1"/>
+    </row>
+    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B140" s="159">
-        <f>SUM(B136:B139)</f>
+      <c r="B146" s="158">
+        <f>SUM(B142:B145)</f>
         <v>0</v>
       </c>
-      <c r="C140" s="87"/>
-    </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="M141" s="88"/>
-    </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="C146" s="87"/>
+    </row>
+    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M147" s="88"/>
+    </row>
+    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5704,32 +5835,44 @@
     <row r="1005" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1006" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1007" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1008" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1009" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1010" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1013" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A106:B107"/>
-    <mergeCell ref="A109:B110"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D45:E45">
+    <sortCondition ref="E44:E45"/>
+  </sortState>
+  <mergeCells count="27">
     <mergeCell ref="B3:D4"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A64:B65"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A68:B69"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A134:C135"/>
-    <mergeCell ref="D64:D65"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A67:B67"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="E64:E65"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A140:C141"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A66:B66"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A110:B111"/>
+    <mergeCell ref="A113:B114"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5770,16 +5913,16 @@
       <c r="C1" s="89"/>
       <c r="D1" s="89"/>
       <c r="E1" s="89"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="234"/>
-      <c r="N1" s="234"/>
-      <c r="O1" s="234"/>
+      <c r="F1" s="277"/>
+      <c r="G1" s="245"/>
+      <c r="H1" s="245"/>
+      <c r="I1" s="245"/>
+      <c r="J1" s="245"/>
+      <c r="K1" s="245"/>
+      <c r="L1" s="245"/>
+      <c r="M1" s="245"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="245"/>
       <c r="P1" s="89"/>
       <c r="Q1" s="89"/>
     </row>
@@ -5803,7 +5946,7 @@
       </c>
       <c r="M2" s="89"/>
       <c r="N2" s="89"/>
-      <c r="O2" s="189">
+      <c r="O2" s="188">
         <v>3000000</v>
       </c>
       <c r="P2" s="91"/>
@@ -5832,80 +5975,80 @@
       <c r="Q3" s="93"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="258" t="s">
+      <c r="A4" s="284" t="s">
         <v>58</v>
       </c>
-      <c r="B4" s="247" t="s">
+      <c r="B4" s="273" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="252" t="s">
+      <c r="C4" s="278" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="252" t="s">
+      <c r="D4" s="278" t="s">
         <v>61</v>
       </c>
-      <c r="E4" s="256" t="s">
+      <c r="E4" s="282" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="252" t="s">
+      <c r="F4" s="278" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="252" t="s">
+      <c r="G4" s="278" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="252" t="s">
+      <c r="H4" s="278" t="s">
         <v>65</v>
       </c>
-      <c r="I4" s="256" t="s">
+      <c r="I4" s="282" t="s">
         <v>66</v>
       </c>
-      <c r="J4" s="257" t="s">
+      <c r="J4" s="283" t="s">
         <v>67</v>
       </c>
-      <c r="K4" s="245" t="s">
+      <c r="K4" s="271" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="249" t="s">
+      <c r="L4" s="275" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="245" t="s">
+      <c r="M4" s="271" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="253" t="s">
+      <c r="N4" s="279" t="s">
         <v>71</v>
       </c>
       <c r="O4" s="94" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="255" t="s">
+      <c r="P4" s="281" t="s">
         <v>73</v>
       </c>
-      <c r="Q4" s="249" t="s">
+      <c r="Q4" s="275" t="s">
         <v>74</v>
       </c>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="250"/>
-      <c r="B5" s="248"/>
-      <c r="C5" s="250"/>
-      <c r="D5" s="250"/>
-      <c r="E5" s="246"/>
-      <c r="F5" s="250"/>
-      <c r="G5" s="250"/>
-      <c r="H5" s="250"/>
-      <c r="I5" s="246"/>
-      <c r="J5" s="246"/>
-      <c r="K5" s="246"/>
-      <c r="L5" s="250"/>
-      <c r="M5" s="246"/>
-      <c r="N5" s="254"/>
+      <c r="A5" s="276"/>
+      <c r="B5" s="274"/>
+      <c r="C5" s="276"/>
+      <c r="D5" s="276"/>
+      <c r="E5" s="272"/>
+      <c r="F5" s="276"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="272"/>
+      <c r="J5" s="272"/>
+      <c r="K5" s="272"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="272"/>
+      <c r="N5" s="280"/>
       <c r="O5" s="95" t="str">
         <f>RESUMEN!B9</f>
-        <v>VTO 15/09</v>
-      </c>
-      <c r="P5" s="248"/>
-      <c r="Q5" s="250"/>
+        <v>VTO 15/10</v>
+      </c>
+      <c r="P5" s="274"/>
+      <c r="Q5" s="276"/>
     </row>
     <row r="6" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -5927,19 +6070,19 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G6" s="98">
-        <v>64929.01</v>
+        <v>33000.01</v>
       </c>
       <c r="H6" s="139">
-        <f>G6</f>
-        <v>64929.01</v>
+        <f t="shared" ref="H6:H12" si="0">G6</f>
+        <v>33000.01</v>
       </c>
       <c r="I6" s="100"/>
       <c r="J6" s="101">
-        <f t="shared" ref="J6:J36" si="0">G6-H6</f>
+        <f t="shared" ref="J6:J36" si="1">G6-H6</f>
         <v>0</v>
       </c>
       <c r="K6" s="101">
-        <f t="shared" ref="K6:K36" si="1">IF(J6&gt;0,J6*3%,0)</f>
+        <f t="shared" ref="K6:K36" si="2">IF(J6&gt;0,J6*3%,0)</f>
         <v>0</v>
       </c>
       <c r="L6" s="98">
@@ -5958,11 +6101,11 @@
         <v>33000.01</v>
       </c>
       <c r="P6" s="107">
-        <f t="shared" ref="P6:P36" si="2">ROUND(O6*6% + O6,0) + R6</f>
+        <f t="shared" ref="P6:P36" si="3">ROUND(O6*6% + O6,0) + R6</f>
         <v>34980.01</v>
       </c>
       <c r="Q6" s="127">
-        <f t="shared" ref="Q6:Q36" si="3">ROUND(O6*3%,0) + O6</f>
+        <f t="shared" ref="Q6:Q36" si="4">ROUND(O6*3%,0) + O6</f>
         <v>33990.01</v>
       </c>
       <c r="R6" s="60">
@@ -5973,60 +6116,60 @@
       <c r="A7" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B7" s="178">
+      <c r="B7" s="177">
         <v>2</v>
       </c>
-      <c r="C7" s="179" t="s">
+      <c r="C7" s="178" t="s">
         <v>80</v>
       </c>
-      <c r="D7" s="179" t="s">
+      <c r="D7" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="180"/>
-      <c r="F7" s="181">
+      <c r="E7" s="179"/>
+      <c r="F7" s="180">
         <v>0.9</v>
       </c>
-      <c r="G7" s="147">
+      <c r="G7" s="146">
         <v>27000.02</v>
       </c>
       <c r="H7" s="139">
-        <f>G7</f>
+        <f t="shared" si="0"/>
         <v>27000.02</v>
       </c>
       <c r="I7" s="100"/>
-      <c r="J7" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K7" s="148">
+      <c r="J7" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L7" s="147">
-        <f t="shared" ref="L7:L34" si="4">O$3*F7%</f>
+      <c r="K7" s="147">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
+      <c r="L7" s="146">
+        <f t="shared" ref="L7:L34" si="5">O$3*F7%</f>
+        <v>0</v>
+      </c>
       <c r="M7" s="101">
-        <f t="shared" ref="M7:M34" si="5">O$2*F7%</f>
+        <f t="shared" ref="M7:M34" si="6">O$2*F7%</f>
         <v>27000.000000000004</v>
       </c>
-      <c r="N7" s="149">
+      <c r="N7" s="148">
         <v>0</v>
       </c>
-      <c r="O7" s="150">
-        <f t="shared" ref="O7:O34" si="6">ROUND(SUM(J7:N7),0) + R7</f>
+      <c r="O7" s="149">
+        <f t="shared" ref="O7:O34" si="7">ROUND(SUM(J7:N7),0) + R7</f>
         <v>27000.02</v>
       </c>
-      <c r="P7" s="151">
-        <f t="shared" si="2"/>
+      <c r="P7" s="150">
+        <f t="shared" si="3"/>
         <v>28620.02</v>
       </c>
-      <c r="Q7" s="152">
-        <f t="shared" si="3"/>
+      <c r="Q7" s="151">
+        <f t="shared" si="4"/>
         <v>27810.02</v>
       </c>
       <c r="R7" s="60">
-        <f t="shared" ref="R7:R35" si="7">R6+0.01</f>
+        <f t="shared" ref="R7:R35" si="8">R6+0.01</f>
         <v>0.02</v>
       </c>
       <c r="S7" s="60"/>
@@ -6035,62 +6178,62 @@
       <c r="A8" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="178">
+      <c r="B8" s="177">
         <v>3</v>
       </c>
-      <c r="C8" s="179" t="s">
+      <c r="C8" s="178" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="179" t="s">
+      <c r="D8" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="180" t="s">
+      <c r="E8" s="179" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="181">
+      <c r="F8" s="180">
         <v>0.8</v>
       </c>
-      <c r="G8" s="147">
-        <v>24000.03</v>
+      <c r="G8" s="146">
+        <v>24720.03</v>
       </c>
       <c r="H8" s="139">
-        <f>G8</f>
-        <v>24000.03</v>
+        <f t="shared" si="0"/>
+        <v>24720.03</v>
       </c>
       <c r="I8" s="100"/>
-      <c r="J8" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="148">
+      <c r="J8" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L8" s="147">
+      <c r="K8" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="101">
+        <f t="shared" si="6"/>
+        <v>24000</v>
+      </c>
+      <c r="N8" s="148">
+        <v>0</v>
+      </c>
+      <c r="O8" s="149">
+        <f t="shared" si="7"/>
+        <v>24000.03</v>
+      </c>
+      <c r="P8" s="150">
+        <f t="shared" si="3"/>
+        <v>25440.03</v>
+      </c>
+      <c r="Q8" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="101">
-        <f t="shared" si="5"/>
-        <v>24000</v>
-      </c>
-      <c r="N8" s="149">
-        <v>0</v>
-      </c>
-      <c r="O8" s="150">
-        <f t="shared" si="6"/>
-        <v>24000.03</v>
-      </c>
-      <c r="P8" s="151">
-        <f t="shared" si="2"/>
-        <v>25440.03</v>
-      </c>
-      <c r="Q8" s="152">
-        <f t="shared" si="3"/>
         <v>24720.03</v>
       </c>
       <c r="R8" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.03</v>
       </c>
     </row>
@@ -6098,60 +6241,60 @@
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="178">
+      <c r="B9" s="177">
         <v>4</v>
       </c>
-      <c r="C9" s="179" t="s">
+      <c r="C9" s="178" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="179" t="s">
+      <c r="D9" s="178" t="s">
         <v>87</v>
       </c>
-      <c r="E9" s="180"/>
-      <c r="F9" s="181">
+      <c r="E9" s="179"/>
+      <c r="F9" s="180">
         <v>0.8</v>
       </c>
-      <c r="G9" s="147">
+      <c r="G9" s="146">
         <v>24000.04</v>
       </c>
       <c r="H9" s="139">
-        <f>G9</f>
+        <f t="shared" si="0"/>
         <v>24000.04</v>
       </c>
       <c r="I9" s="100"/>
-      <c r="J9" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="148">
+      <c r="J9" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L9" s="147">
+      <c r="K9" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="101">
+        <f t="shared" si="6"/>
+        <v>24000</v>
+      </c>
+      <c r="N9" s="148">
+        <v>0</v>
+      </c>
+      <c r="O9" s="149">
+        <f t="shared" si="7"/>
+        <v>24000.04</v>
+      </c>
+      <c r="P9" s="150">
+        <f t="shared" si="3"/>
+        <v>25440.04</v>
+      </c>
+      <c r="Q9" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="101">
-        <f t="shared" si="5"/>
-        <v>24000</v>
-      </c>
-      <c r="N9" s="149">
-        <v>0</v>
-      </c>
-      <c r="O9" s="150">
-        <f t="shared" si="6"/>
-        <v>24000.04</v>
-      </c>
-      <c r="P9" s="151">
-        <f t="shared" si="2"/>
-        <v>25440.04</v>
-      </c>
-      <c r="Q9" s="152">
-        <f t="shared" si="3"/>
         <v>24720.04</v>
       </c>
       <c r="R9" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
     </row>
@@ -6159,62 +6302,62 @@
       <c r="A10" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="178">
+      <c r="B10" s="177">
         <v>5</v>
       </c>
-      <c r="C10" s="179" t="s">
+      <c r="C10" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="179" t="s">
+      <c r="D10" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="180" t="s">
+      <c r="E10" s="179" t="s">
         <v>89</v>
       </c>
-      <c r="F10" s="181">
+      <c r="F10" s="180">
         <v>0.5</v>
       </c>
-      <c r="G10" s="147">
-        <v>100940.05</v>
+      <c r="G10" s="146">
+        <v>15000.05</v>
       </c>
       <c r="H10" s="139">
-        <f>G10</f>
-        <v>100940.05</v>
+        <f t="shared" si="0"/>
+        <v>15000.05</v>
       </c>
       <c r="I10" s="100"/>
-      <c r="J10" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K10" s="148">
+      <c r="J10" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L10" s="147">
+      <c r="K10" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M10" s="101">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="N10" s="148">
+        <v>0</v>
+      </c>
+      <c r="O10" s="149">
+        <f t="shared" si="7"/>
+        <v>15000.05</v>
+      </c>
+      <c r="P10" s="150">
+        <f t="shared" si="3"/>
+        <v>15900.05</v>
+      </c>
+      <c r="Q10" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="101">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="N10" s="149">
-        <v>0</v>
-      </c>
-      <c r="O10" s="150">
-        <f t="shared" si="6"/>
-        <v>15000.05</v>
-      </c>
-      <c r="P10" s="151">
-        <f t="shared" si="2"/>
-        <v>15900.05</v>
-      </c>
-      <c r="Q10" s="152">
-        <f t="shared" si="3"/>
         <v>15450.05</v>
       </c>
       <c r="R10" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.05</v>
       </c>
     </row>
@@ -6222,60 +6365,60 @@
       <c r="A11" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="178">
+      <c r="B11" s="177">
         <v>6</v>
       </c>
-      <c r="C11" s="179" t="s">
+      <c r="C11" s="178" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="179" t="s">
+      <c r="D11" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="182"/>
-      <c r="F11" s="181">
+      <c r="E11" s="181"/>
+      <c r="F11" s="180">
         <v>0.5</v>
       </c>
-      <c r="G11" s="147">
+      <c r="G11" s="146">
         <v>15000.06</v>
       </c>
       <c r="H11" s="139">
-        <f>G11</f>
+        <f t="shared" si="0"/>
         <v>15000.06</v>
       </c>
       <c r="I11" s="100"/>
-      <c r="J11" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K11" s="148">
+      <c r="J11" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L11" s="147">
+      <c r="K11" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L11" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="101">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="N11" s="148">
+        <v>0</v>
+      </c>
+      <c r="O11" s="149">
+        <f t="shared" si="7"/>
+        <v>15000.06</v>
+      </c>
+      <c r="P11" s="150">
+        <f t="shared" si="3"/>
+        <v>15900.06</v>
+      </c>
+      <c r="Q11" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="101">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="N11" s="149">
-        <v>0</v>
-      </c>
-      <c r="O11" s="150">
-        <f t="shared" si="6"/>
-        <v>15000.06</v>
-      </c>
-      <c r="P11" s="151">
-        <f t="shared" si="2"/>
-        <v>15900.06</v>
-      </c>
-      <c r="Q11" s="152">
-        <f t="shared" si="3"/>
         <v>15450.06</v>
       </c>
       <c r="R11" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
@@ -6283,62 +6426,62 @@
       <c r="A12" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="178">
+      <c r="B12" s="177">
         <v>7</v>
       </c>
-      <c r="C12" s="179" t="s">
+      <c r="C12" s="178" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="179" t="s">
+      <c r="D12" s="178" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="180" t="s">
+      <c r="E12" s="179" t="s">
         <v>93</v>
       </c>
-      <c r="F12" s="181">
+      <c r="F12" s="180">
         <v>0.5</v>
       </c>
-      <c r="G12" s="147">
-        <v>15000.07</v>
+      <c r="G12" s="146">
+        <v>15450.07</v>
       </c>
       <c r="H12" s="139">
-        <f>G12</f>
-        <v>15000.07</v>
+        <f t="shared" si="0"/>
+        <v>15450.07</v>
       </c>
       <c r="I12" s="100"/>
-      <c r="J12" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="148">
+      <c r="J12" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L12" s="147">
+      <c r="K12" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="101">
+        <f t="shared" si="6"/>
+        <v>15000</v>
+      </c>
+      <c r="N12" s="148">
+        <v>0</v>
+      </c>
+      <c r="O12" s="149">
+        <f t="shared" si="7"/>
+        <v>15000.07</v>
+      </c>
+      <c r="P12" s="150">
+        <f t="shared" si="3"/>
+        <v>15900.07</v>
+      </c>
+      <c r="Q12" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="101">
-        <f t="shared" si="5"/>
-        <v>15000</v>
-      </c>
-      <c r="N12" s="149">
-        <v>0</v>
-      </c>
-      <c r="O12" s="150">
-        <f t="shared" si="6"/>
-        <v>15000.07</v>
-      </c>
-      <c r="P12" s="151">
-        <f t="shared" si="2"/>
-        <v>15900.07</v>
-      </c>
-      <c r="Q12" s="152">
-        <f t="shared" si="3"/>
         <v>15450.07</v>
       </c>
       <c r="R12" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
@@ -6346,59 +6489,60 @@
       <c r="A13" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B13" s="265" t="s">
+      <c r="B13" s="223" t="s">
         <v>95</v>
       </c>
-      <c r="C13" s="266">
+      <c r="C13" s="224">
         <v>1</v>
       </c>
-      <c r="D13" s="266" t="s">
+      <c r="D13" s="224" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="267" t="s">
+      <c r="E13" s="225" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="268">
+      <c r="F13" s="226">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G13" s="269">
-        <v>200000</v>
-      </c>
-      <c r="H13" s="276">
-        <v>200000</v>
-      </c>
-      <c r="I13" s="270"/>
-      <c r="J13" s="271">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K13" s="271">
+      <c r="G13" s="227">
+        <v>132000.07999999999</v>
+      </c>
+      <c r="H13" s="234">
+        <f>G13</f>
+        <v>132000.07999999999</v>
+      </c>
+      <c r="I13" s="228"/>
+      <c r="J13" s="229">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L13" s="269">
+      <c r="K13" s="229">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="227">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="229">
+        <f t="shared" si="6"/>
+        <v>132000</v>
+      </c>
+      <c r="N13" s="230"/>
+      <c r="O13" s="231">
+        <f t="shared" si="7"/>
+        <v>132000.07999999999</v>
+      </c>
+      <c r="P13" s="232">
+        <f t="shared" si="3"/>
+        <v>139920.07999999999</v>
+      </c>
+      <c r="Q13" s="233">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="271">
-        <f t="shared" si="5"/>
-        <v>132000</v>
-      </c>
-      <c r="N13" s="272"/>
-      <c r="O13" s="273">
-        <f t="shared" si="6"/>
-        <v>132000.07999999999</v>
-      </c>
-      <c r="P13" s="274">
-        <f t="shared" si="2"/>
-        <v>139920.07999999999</v>
-      </c>
-      <c r="Q13" s="275">
-        <f t="shared" si="3"/>
         <v>135960.07999999999</v>
       </c>
       <c r="R13" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.08</v>
       </c>
     </row>
@@ -6410,7 +6554,7 @@
         <v>98</v>
       </c>
       <c r="C14" s="120">
-        <f t="shared" ref="C14:C34" si="8">C13+1</f>
+        <f t="shared" ref="C14:C34" si="9">C13+1</f>
         <v>2</v>
       </c>
       <c r="D14" s="120" t="s">
@@ -6429,41 +6573,41 @@
       </c>
       <c r="I14" s="100"/>
       <c r="J14" s="101">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.13000000000465661</v>
       </c>
       <c r="K14" s="101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9000000001396984E-3</v>
       </c>
       <c r="L14" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M14" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N14" s="102">
         <v>0</v>
       </c>
       <c r="O14" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>135000.09</v>
       </c>
       <c r="P14" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143100.09</v>
       </c>
       <c r="Q14" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>139050.09</v>
       </c>
       <c r="R14" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.09</v>
       </c>
-      <c r="U14" s="156" t="s">
+      <c r="U14" s="155" t="s">
         <v>99</v>
       </c>
     </row>
@@ -6475,7 +6619,7 @@
         <v>101</v>
       </c>
       <c r="C15" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="D15" s="120" t="s">
@@ -6488,46 +6632,46 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="98">
-        <v>269653.09999999998</v>
-      </c>
-      <c r="H15" s="175">
-        <f>220593-H10</f>
-        <v>119652.95</v>
+        <v>289500.09999999998</v>
+      </c>
+      <c r="H15" s="174">
+        <f>150000+154500-H10</f>
+        <v>289499.95</v>
       </c>
       <c r="I15" s="100"/>
       <c r="J15" s="101">
-        <f t="shared" si="0"/>
-        <v>150000.14999999997</v>
+        <f t="shared" si="1"/>
+        <v>0.1499999999650754</v>
       </c>
       <c r="K15" s="101">
-        <f t="shared" si="1"/>
-        <v>4500.0044999999991</v>
+        <f t="shared" si="2"/>
+        <v>4.4999999989522622E-3</v>
       </c>
       <c r="L15" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M15" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N15" s="102">
         <v>0</v>
       </c>
       <c r="O15" s="126">
-        <f t="shared" si="6"/>
-        <v>289500.09999999998</v>
+        <f t="shared" si="7"/>
+        <v>135000.1</v>
       </c>
       <c r="P15" s="107">
-        <f t="shared" si="2"/>
-        <v>306870.09999999998</v>
+        <f t="shared" si="3"/>
+        <v>143100.1</v>
       </c>
       <c r="Q15" s="127">
-        <f t="shared" si="3"/>
-        <v>298185.09999999998</v>
+        <f t="shared" si="4"/>
+        <v>139050.1</v>
       </c>
       <c r="R15" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
@@ -6539,7 +6683,7 @@
         <v>104</v>
       </c>
       <c r="C16" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
       <c r="D16" s="120" t="s">
@@ -6560,38 +6704,38 @@
       </c>
       <c r="I16" s="100"/>
       <c r="J16" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K16" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K16" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L16" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M16" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N16" s="102">
         <v>0</v>
       </c>
       <c r="O16" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>93000.11</v>
       </c>
       <c r="P16" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>98580.11</v>
       </c>
       <c r="Q16" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>95790.11</v>
       </c>
       <c r="R16" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.10999999999999999</v>
       </c>
     </row>
@@ -6599,60 +6743,62 @@
       <c r="A17" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="178" t="s">
+      <c r="B17" s="177" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="179">
+      <c r="C17" s="178">
+        <f t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="D17" s="178" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" s="179" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="180">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G17" s="146">
+        <v>260498.12</v>
+      </c>
+      <c r="H17" s="139">
+        <v>121000</v>
+      </c>
+      <c r="I17" s="100"/>
+      <c r="J17" s="147">
+        <f t="shared" si="1"/>
+        <v>139498.12</v>
+      </c>
+      <c r="K17" s="147">
+        <f t="shared" si="2"/>
+        <v>4184.9435999999996</v>
+      </c>
+      <c r="L17" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M17" s="147">
+        <f t="shared" si="6"/>
+        <v>132000</v>
+      </c>
+      <c r="N17" s="148">
+        <v>0</v>
+      </c>
+      <c r="O17" s="149">
+        <f t="shared" si="7"/>
+        <v>275683.12</v>
+      </c>
+      <c r="P17" s="150">
+        <f t="shared" si="3"/>
+        <v>292224.12</v>
+      </c>
+      <c r="Q17" s="151">
+        <f t="shared" si="4"/>
+        <v>283953.12</v>
+      </c>
+      <c r="R17" s="60">
         <f t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="D17" s="179" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" s="180" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="181">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G17" s="147">
-        <v>117389.12</v>
-      </c>
-      <c r="H17" s="139"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="148">
-        <f t="shared" si="0"/>
-        <v>117389.12</v>
-      </c>
-      <c r="K17" s="148">
-        <f t="shared" si="1"/>
-        <v>3521.6735999999996</v>
-      </c>
-      <c r="L17" s="147">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="148">
-        <f t="shared" si="5"/>
-        <v>132000</v>
-      </c>
-      <c r="N17" s="149">
-        <v>0</v>
-      </c>
-      <c r="O17" s="150">
-        <f t="shared" si="6"/>
-        <v>252911.12</v>
-      </c>
-      <c r="P17" s="151">
-        <f t="shared" si="2"/>
-        <v>268086.12</v>
-      </c>
-      <c r="Q17" s="152">
-        <f t="shared" si="3"/>
-        <v>260498.12</v>
-      </c>
-      <c r="R17" s="60">
-        <f t="shared" si="7"/>
         <v>0.11999999999999998</v>
       </c>
     </row>
@@ -6660,62 +6806,60 @@
       <c r="A18" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="178" t="s">
+      <c r="B18" s="177" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="179">
+      <c r="C18" s="178">
+        <f t="shared" si="9"/>
+        <v>6</v>
+      </c>
+      <c r="D18" s="178" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="179" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="180">
+        <v>4.5</v>
+      </c>
+      <c r="G18" s="146">
+        <v>134974.13</v>
+      </c>
+      <c r="H18" s="139"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="147">
+        <f t="shared" si="1"/>
+        <v>134974.13</v>
+      </c>
+      <c r="K18" s="147">
+        <f t="shared" si="2"/>
+        <v>4049.2239</v>
+      </c>
+      <c r="L18" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="147">
+        <f t="shared" si="6"/>
+        <v>135000</v>
+      </c>
+      <c r="N18" s="148">
+        <v>0</v>
+      </c>
+      <c r="O18" s="149">
+        <f t="shared" si="7"/>
+        <v>274023.13</v>
+      </c>
+      <c r="P18" s="150">
+        <f t="shared" si="3"/>
+        <v>290465.13</v>
+      </c>
+      <c r="Q18" s="151">
+        <f t="shared" si="4"/>
+        <v>282244.13</v>
+      </c>
+      <c r="R18" s="60">
         <f t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="D18" s="179" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="180" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="181">
-        <v>4.5</v>
-      </c>
-      <c r="G18" s="147">
-        <v>134974.13</v>
-      </c>
-      <c r="H18" s="139">
-        <v>135000</v>
-      </c>
-      <c r="I18" s="100"/>
-      <c r="J18" s="148">
-        <f t="shared" si="0"/>
-        <v>-25.869999999995343</v>
-      </c>
-      <c r="K18" s="148">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="147">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="148">
-        <f t="shared" si="5"/>
-        <v>135000</v>
-      </c>
-      <c r="N18" s="149">
-        <v>0</v>
-      </c>
-      <c r="O18" s="150">
-        <f t="shared" si="6"/>
-        <v>134974.13</v>
-      </c>
-      <c r="P18" s="151">
-        <f t="shared" si="2"/>
-        <v>143073.13</v>
-      </c>
-      <c r="Q18" s="152">
-        <f t="shared" si="3"/>
-        <v>139023.13</v>
-      </c>
-      <c r="R18" s="60">
-        <f t="shared" si="7"/>
         <v>0.12999999999999998</v>
       </c>
     </row>
@@ -6727,7 +6871,7 @@
         <v>115</v>
       </c>
       <c r="C19" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
       <c r="D19" s="120" t="s">
@@ -6746,38 +6890,38 @@
       </c>
       <c r="I19" s="100"/>
       <c r="J19" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K19" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L19" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M19" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N19" s="102">
         <v>0</v>
       </c>
       <c r="O19" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>135000.14000000001</v>
       </c>
       <c r="P19" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143100.14000000001</v>
       </c>
       <c r="Q19" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>139050.14000000001</v>
       </c>
       <c r="R19" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.13999999999999999</v>
       </c>
     </row>
@@ -6789,7 +6933,7 @@
         <v>117</v>
       </c>
       <c r="C20" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
       <c r="D20" s="120" t="s">
@@ -6800,45 +6944,46 @@
         <v>3.1</v>
       </c>
       <c r="G20" s="98">
-        <v>93000.15</v>
+        <v>92210.15</v>
       </c>
       <c r="H20" s="139">
-        <v>93790</v>
+        <f>G20</f>
+        <v>92210.15</v>
       </c>
       <c r="I20" s="100"/>
       <c r="J20" s="101">
-        <f t="shared" si="0"/>
-        <v>-789.85000000000582</v>
-      </c>
-      <c r="K20" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K20" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L20" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M20" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N20" s="102">
         <v>0</v>
       </c>
       <c r="O20" s="126">
-        <f t="shared" si="6"/>
-        <v>92210.15</v>
+        <f t="shared" si="7"/>
+        <v>93000.15</v>
       </c>
       <c r="P20" s="107">
-        <f t="shared" si="2"/>
-        <v>97743.15</v>
+        <f t="shared" si="3"/>
+        <v>98580.15</v>
       </c>
       <c r="Q20" s="127">
-        <f t="shared" si="3"/>
-        <v>94976.15</v>
+        <f t="shared" si="4"/>
+        <v>95790.15</v>
       </c>
       <c r="R20" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.15</v>
       </c>
     </row>
@@ -6850,7 +6995,7 @@
         <v>120</v>
       </c>
       <c r="C21" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="D21" s="120" t="s">
@@ -6871,38 +7016,38 @@
       </c>
       <c r="I21" s="100"/>
       <c r="J21" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K21" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L21" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M21" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>132000</v>
       </c>
       <c r="N21" s="102">
         <v>0</v>
       </c>
       <c r="O21" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>132000.16</v>
       </c>
       <c r="P21" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139920.16</v>
       </c>
       <c r="Q21" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>135960.16</v>
       </c>
       <c r="R21" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.16</v>
       </c>
       <c r="T21" s="106"/>
@@ -6915,7 +7060,7 @@
         <v>123</v>
       </c>
       <c r="C22" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="D22" s="120" t="s">
@@ -6928,49 +7073,50 @@
         <v>4.5</v>
       </c>
       <c r="G22" s="99">
-        <v>262992.17</v>
+        <v>266832.17</v>
       </c>
       <c r="H22" s="139">
-        <v>135000</v>
+        <f>G22</f>
+        <v>266832.17</v>
       </c>
       <c r="I22" s="100"/>
       <c r="J22" s="101">
-        <f t="shared" si="0"/>
-        <v>127992.16999999998</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="K22" s="101">
-        <f t="shared" si="1"/>
-        <v>3839.7650999999992</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L22" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M22" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N22" s="102">
         <v>0</v>
       </c>
       <c r="O22" s="126">
-        <f t="shared" si="6"/>
-        <v>266832.17</v>
+        <f t="shared" si="7"/>
+        <v>135000.17000000001</v>
       </c>
       <c r="P22" s="107">
-        <f t="shared" si="2"/>
-        <v>282842.17</v>
+        <f t="shared" si="3"/>
+        <v>143100.17000000001</v>
       </c>
       <c r="Q22" s="127">
-        <f t="shared" si="3"/>
-        <v>274837.17</v>
+        <f t="shared" si="4"/>
+        <v>139050.17000000001</v>
       </c>
       <c r="R22" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.17</v>
       </c>
-      <c r="T22" s="155"/>
-      <c r="U22" s="183" t="s">
+      <c r="T22" s="154"/>
+      <c r="U22" s="182" t="s">
         <v>125</v>
       </c>
     </row>
@@ -6982,7 +7128,7 @@
         <v>127</v>
       </c>
       <c r="C23" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="D23" s="120" t="s">
@@ -6992,7 +7138,7 @@
       <c r="F23" s="97">
         <v>4.5</v>
       </c>
-      <c r="G23" s="147">
+      <c r="G23" s="146">
         <v>135000.18</v>
       </c>
       <c r="H23" s="139">
@@ -7000,42 +7146,42 @@
         <v>135000.18</v>
       </c>
       <c r="I23" s="100"/>
-      <c r="J23" s="148">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="148">
+      <c r="J23" s="147">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L23" s="147">
+      <c r="K23" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M23" s="101">
+        <f t="shared" si="6"/>
+        <v>135000</v>
+      </c>
+      <c r="N23" s="148">
+        <v>0</v>
+      </c>
+      <c r="O23" s="149">
+        <f t="shared" si="7"/>
+        <v>135000.18</v>
+      </c>
+      <c r="P23" s="150">
+        <f t="shared" si="3"/>
+        <v>143100.18</v>
+      </c>
+      <c r="Q23" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M23" s="101">
-        <f t="shared" si="5"/>
-        <v>135000</v>
-      </c>
-      <c r="N23" s="149">
-        <v>0</v>
-      </c>
-      <c r="O23" s="150">
-        <f t="shared" si="6"/>
-        <v>135000.18</v>
-      </c>
-      <c r="P23" s="151">
-        <f t="shared" si="2"/>
-        <v>143100.18</v>
-      </c>
-      <c r="Q23" s="152">
-        <f t="shared" si="3"/>
         <v>139050.18</v>
       </c>
       <c r="R23" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.18000000000000002</v>
       </c>
-      <c r="T23" s="155"/>
+      <c r="T23" s="154"/>
     </row>
     <row r="24" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
@@ -7045,7 +7191,7 @@
         <v>129</v>
       </c>
       <c r="C24" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="D24" s="120" t="s">
@@ -7058,116 +7204,116 @@
         <v>3.1</v>
       </c>
       <c r="G24" s="98">
-        <v>92201.19</v>
+        <v>95790.19</v>
       </c>
       <c r="H24" s="139">
-        <f>116201-H8</f>
-        <v>92200.97</v>
+        <f>117720-H8</f>
+        <v>92999.97</v>
       </c>
       <c r="I24" s="100"/>
       <c r="J24" s="101">
-        <f t="shared" si="0"/>
-        <v>0.22000000000116415</v>
+        <f t="shared" si="1"/>
+        <v>2790.2200000000012</v>
       </c>
       <c r="K24" s="101">
-        <f t="shared" si="1"/>
-        <v>6.6000000000349243E-3</v>
+        <f t="shared" si="2"/>
+        <v>83.706600000000037</v>
       </c>
       <c r="L24" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M24" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N24" s="102">
         <v>0</v>
       </c>
       <c r="O24" s="126">
-        <f t="shared" si="6"/>
-        <v>93000.19</v>
+        <f t="shared" si="7"/>
+        <v>95874.19</v>
       </c>
       <c r="P24" s="107">
-        <f t="shared" si="2"/>
-        <v>98580.19</v>
+        <f t="shared" si="3"/>
+        <v>101627.19</v>
       </c>
       <c r="Q24" s="127">
-        <f t="shared" si="3"/>
-        <v>95790.19</v>
+        <f t="shared" si="4"/>
+        <v>98750.19</v>
       </c>
       <c r="R24" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.19000000000000003</v>
       </c>
-      <c r="T24" s="155"/>
+      <c r="T24" s="154"/>
     </row>
     <row r="25" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="178" t="s">
+      <c r="B25" s="177" t="s">
         <v>131</v>
       </c>
-      <c r="C25" s="179">
-        <f t="shared" si="8"/>
+      <c r="C25" s="178">
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="D25" s="179" t="s">
+      <c r="D25" s="178" t="s">
         <v>132</v>
       </c>
-      <c r="E25" s="182"/>
-      <c r="F25" s="181">
+      <c r="E25" s="181"/>
+      <c r="F25" s="180">
         <v>4.4000000000000004</v>
       </c>
-      <c r="G25" s="147">
-        <v>369157.2</v>
+      <c r="G25" s="146">
+        <v>232072.2</v>
       </c>
       <c r="H25" s="139">
-        <f>136000*2</f>
-        <v>272000</v>
+        <f>132000+100000+2915</f>
+        <v>234915</v>
       </c>
       <c r="I25" s="100"/>
       <c r="J25" s="100">
-        <f t="shared" si="0"/>
-        <v>97157.200000000012</v>
-      </c>
-      <c r="K25" s="148">
         <f t="shared" si="1"/>
-        <v>2914.7160000000003</v>
-      </c>
-      <c r="L25" s="147">
+        <v>-2842.7999999999884</v>
+      </c>
+      <c r="K25" s="147">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="146">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="101">
+        <f t="shared" si="6"/>
+        <v>132000</v>
+      </c>
+      <c r="N25" s="148">
+        <v>0</v>
+      </c>
+      <c r="O25" s="149">
+        <f t="shared" si="7"/>
+        <v>129157.2</v>
+      </c>
+      <c r="P25" s="150">
+        <f t="shared" si="3"/>
+        <v>136907.20000000001</v>
+      </c>
+      <c r="Q25" s="151">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="101">
-        <f t="shared" si="5"/>
-        <v>132000</v>
-      </c>
-      <c r="N25" s="149">
-        <v>0</v>
-      </c>
-      <c r="O25" s="150">
-        <f t="shared" si="6"/>
-        <v>232072.2</v>
-      </c>
-      <c r="P25" s="151">
-        <f t="shared" si="2"/>
-        <v>245997.2</v>
-      </c>
-      <c r="Q25" s="152">
-        <f t="shared" si="3"/>
-        <v>239034.2</v>
+        <v>133032.20000000001</v>
       </c>
       <c r="R25" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.20000000000000004</v>
       </c>
-      <c r="T25" s="156" t="s">
+      <c r="T25" s="155" t="s">
         <v>133</v>
       </c>
-      <c r="U25" s="177"/>
-      <c r="V25" s="156"/>
+      <c r="U25" s="176"/>
+      <c r="V25" s="155"/>
     </row>
     <row r="26" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
@@ -7177,7 +7323,7 @@
         <v>135</v>
       </c>
       <c r="C26" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="D26" s="120" t="s">
@@ -7190,49 +7336,49 @@
         <v>4.5</v>
       </c>
       <c r="G26" s="98">
-        <v>265618.21000000002</v>
+        <v>135000.21</v>
       </c>
       <c r="H26" s="139">
-        <f>330547-H6</f>
-        <v>265617.99</v>
+        <f>168000-H6</f>
+        <v>134999.99</v>
       </c>
       <c r="I26" s="100"/>
       <c r="J26" s="101">
-        <f t="shared" si="0"/>
-        <v>0.22000000003026798</v>
+        <f t="shared" si="1"/>
+        <v>0.22000000000116415</v>
       </c>
       <c r="K26" s="101">
-        <f t="shared" si="1"/>
-        <v>6.6000000009080392E-3</v>
+        <f t="shared" si="2"/>
+        <v>6.6000000000349243E-3</v>
       </c>
       <c r="L26" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M26" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N26" s="102">
         <v>0</v>
       </c>
       <c r="O26" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>135000.21</v>
       </c>
       <c r="P26" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143100.21</v>
       </c>
       <c r="Q26" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>139050.21</v>
       </c>
       <c r="R26" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
-      <c r="T26" s="155"/>
+      <c r="T26" s="154"/>
     </row>
     <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
@@ -7242,7 +7388,7 @@
         <v>138</v>
       </c>
       <c r="C27" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="D27" s="120" t="s">
@@ -7255,49 +7401,49 @@
         <v>4.5</v>
       </c>
       <c r="G27" s="98">
-        <v>280129.21999999997</v>
+        <v>297736.21999999997</v>
       </c>
       <c r="H27" s="139">
-        <f>131040+14513-H12</f>
-        <v>130552.93</v>
+        <f>135000-H12</f>
+        <v>119549.93</v>
       </c>
       <c r="I27" s="100"/>
       <c r="J27" s="101">
-        <f t="shared" si="0"/>
-        <v>149576.28999999998</v>
+        <f t="shared" si="1"/>
+        <v>178186.28999999998</v>
       </c>
       <c r="K27" s="101">
-        <f t="shared" si="1"/>
-        <v>4487.2886999999992</v>
+        <f t="shared" si="2"/>
+        <v>5345.5886999999993</v>
       </c>
       <c r="L27" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M27" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N27" s="102">
         <v>0</v>
       </c>
       <c r="O27" s="126">
-        <f t="shared" si="6"/>
-        <v>289064.21999999997</v>
+        <f t="shared" si="7"/>
+        <v>318532.21999999997</v>
       </c>
       <c r="P27" s="107">
-        <f t="shared" si="2"/>
-        <v>306408.21999999997</v>
+        <f t="shared" si="3"/>
+        <v>337644.22</v>
       </c>
       <c r="Q27" s="127">
-        <f t="shared" si="3"/>
-        <v>297736.21999999997</v>
+        <f t="shared" si="4"/>
+        <v>328088.21999999997</v>
       </c>
       <c r="R27" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
-      <c r="T27" s="184"/>
+      <c r="T27" s="183"/>
     </row>
     <row r="28" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
@@ -7307,7 +7453,7 @@
         <v>142</v>
       </c>
       <c r="C28" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="D28" s="120" t="s">
@@ -7320,43 +7466,46 @@
         <v>3.1</v>
       </c>
       <c r="G28" s="98">
-        <v>93000.23</v>
-      </c>
-      <c r="H28" s="139"/>
+        <v>188790.23</v>
+      </c>
+      <c r="H28" s="139">
+        <f>95790+93000</f>
+        <v>188790</v>
+      </c>
       <c r="I28" s="100"/>
       <c r="J28" s="101">
-        <f t="shared" si="0"/>
-        <v>93000.23</v>
+        <f t="shared" si="1"/>
+        <v>0.23000000001047738</v>
       </c>
       <c r="K28" s="101">
-        <f t="shared" si="1"/>
-        <v>2790.0068999999999</v>
+        <f t="shared" si="2"/>
+        <v>6.9000000003143214E-3</v>
       </c>
       <c r="L28" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M28" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N28" s="102">
         <v>0</v>
       </c>
       <c r="O28" s="126">
-        <f t="shared" si="6"/>
-        <v>188790.23</v>
+        <f t="shared" si="7"/>
+        <v>93000.23</v>
       </c>
       <c r="P28" s="107">
-        <f t="shared" si="2"/>
-        <v>200118.23</v>
+        <f t="shared" si="3"/>
+        <v>98580.23</v>
       </c>
       <c r="Q28" s="127">
-        <f t="shared" si="3"/>
-        <v>194454.23</v>
+        <f t="shared" si="4"/>
+        <v>95790.23</v>
       </c>
       <c r="R28" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
     </row>
@@ -7368,7 +7517,7 @@
         <v>146</v>
       </c>
       <c r="C29" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="D29" s="120" t="s">
@@ -7379,46 +7528,46 @@
         <v>6.8</v>
       </c>
       <c r="G29" s="98">
-        <v>204084.24</v>
+        <v>219546.23999999999</v>
       </c>
       <c r="H29" s="139">
-        <f>230991-H7-H11</f>
-        <v>188990.92</v>
+        <f>261550-H7-H11</f>
+        <v>219549.92</v>
       </c>
       <c r="I29" s="100"/>
       <c r="J29" s="101">
-        <f t="shared" si="0"/>
-        <v>15093.319999999978</v>
+        <f t="shared" si="1"/>
+        <v>-3.6800000000221189</v>
       </c>
       <c r="K29" s="101">
-        <f t="shared" si="1"/>
-        <v>452.79959999999932</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="L29" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="101">
+        <f t="shared" si="6"/>
+        <v>204000.00000000003</v>
+      </c>
+      <c r="N29" s="102">
+        <v>26000</v>
+      </c>
+      <c r="O29" s="126">
+        <f t="shared" si="7"/>
+        <v>229996.24</v>
+      </c>
+      <c r="P29" s="107">
+        <f t="shared" si="3"/>
+        <v>243796.24</v>
+      </c>
+      <c r="Q29" s="127">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="101">
-        <f t="shared" si="5"/>
-        <v>204000.00000000003</v>
-      </c>
-      <c r="N29" s="102">
-        <v>0</v>
-      </c>
-      <c r="O29" s="126">
-        <f t="shared" si="6"/>
-        <v>219546.23999999999</v>
-      </c>
-      <c r="P29" s="107">
-        <f t="shared" si="2"/>
-        <v>232719.24</v>
-      </c>
-      <c r="Q29" s="127">
-        <f t="shared" si="3"/>
-        <v>226132.24</v>
+        <v>236896.24</v>
       </c>
       <c r="R29" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
     </row>
@@ -7426,62 +7575,62 @@
       <c r="A30" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="178" t="s">
+      <c r="B30" s="177" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="179">
-        <f t="shared" si="8"/>
+      <c r="C30" s="178">
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="D30" s="179" t="s">
+      <c r="D30" s="178" t="s">
         <v>148</v>
       </c>
-      <c r="E30" s="182"/>
-      <c r="F30" s="181">
+      <c r="E30" s="181"/>
+      <c r="F30" s="180">
         <v>6.9</v>
       </c>
-      <c r="G30" s="147">
-        <v>755474.25</v>
+      <c r="G30" s="146">
+        <v>298035.25</v>
       </c>
       <c r="H30" s="139">
-        <f>250000*2+140000+115444</f>
-        <v>755444</v>
+        <f>207031+91004</f>
+        <v>298035</v>
       </c>
       <c r="I30" s="100"/>
-      <c r="J30" s="148">
-        <f t="shared" si="0"/>
-        <v>30.25</v>
-      </c>
-      <c r="K30" s="148">
+      <c r="J30" s="147">
         <f t="shared" si="1"/>
-        <v>0.90749999999999997</v>
-      </c>
-      <c r="L30" s="147">
-        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="K30" s="147">
+        <f t="shared" si="2"/>
+        <v>7.4999999999999997E-3</v>
+      </c>
+      <c r="L30" s="146">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M30" s="148">
-        <f t="shared" si="5"/>
+      <c r="M30" s="147">
+        <f t="shared" si="6"/>
         <v>207000.00000000003</v>
       </c>
-      <c r="N30" s="149">
+      <c r="N30" s="148">
         <f>73204+17800</f>
         <v>91004</v>
       </c>
-      <c r="O30" s="150">
-        <f t="shared" si="6"/>
-        <v>298035.25</v>
-      </c>
-      <c r="P30" s="151">
-        <f t="shared" si="2"/>
-        <v>315917.25</v>
-      </c>
-      <c r="Q30" s="152">
+      <c r="O30" s="149">
+        <f t="shared" si="7"/>
+        <v>298004.25</v>
+      </c>
+      <c r="P30" s="150">
         <f t="shared" si="3"/>
-        <v>306976.25</v>
+        <v>315885.25</v>
+      </c>
+      <c r="Q30" s="151">
+        <f t="shared" si="4"/>
+        <v>306944.25</v>
       </c>
       <c r="R30" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.25000000000000006</v>
       </c>
     </row>
@@ -7493,7 +7642,7 @@
         <v>149</v>
       </c>
       <c r="C31" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="D31" s="120" t="s">
@@ -7514,38 +7663,38 @@
       </c>
       <c r="I31" s="100"/>
       <c r="J31" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K31" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L31" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M31" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>135000</v>
       </c>
       <c r="N31" s="102">
         <v>0</v>
       </c>
       <c r="O31" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>135000.26</v>
       </c>
       <c r="P31" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>143100.26</v>
       </c>
       <c r="Q31" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>139050.26</v>
       </c>
       <c r="R31" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.26000000000000006</v>
       </c>
     </row>
@@ -7557,7 +7706,7 @@
         <v>152</v>
       </c>
       <c r="C32" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="D32" s="120" t="s">
@@ -7570,45 +7719,45 @@
         <v>3.1</v>
       </c>
       <c r="G32" s="98">
-        <v>182980.27</v>
-      </c>
-      <c r="H32" s="176">
+        <v>185680.27</v>
+      </c>
+      <c r="H32" s="175">
         <v>93000</v>
       </c>
       <c r="I32" s="100"/>
       <c r="J32" s="101">
-        <f t="shared" si="0"/>
-        <v>89980.26999999999</v>
+        <f t="shared" si="1"/>
+        <v>92680.26999999999</v>
       </c>
       <c r="K32" s="101">
-        <f t="shared" si="1"/>
-        <v>2699.4080999999996</v>
+        <f t="shared" si="2"/>
+        <v>2780.4080999999996</v>
       </c>
       <c r="L32" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M32" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N32" s="102">
         <v>0</v>
       </c>
       <c r="O32" s="126">
-        <f t="shared" si="6"/>
-        <v>185680.27</v>
+        <f t="shared" si="7"/>
+        <v>188461.27</v>
       </c>
       <c r="P32" s="107">
-        <f t="shared" si="2"/>
-        <v>196821.27</v>
+        <f t="shared" si="3"/>
+        <v>199769.27</v>
       </c>
       <c r="Q32" s="127">
-        <f t="shared" si="3"/>
-        <v>191250.27</v>
+        <f t="shared" si="4"/>
+        <v>194115.27</v>
       </c>
       <c r="R32" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.27000000000000007</v>
       </c>
     </row>
@@ -7616,57 +7765,57 @@
       <c r="A33" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="191" t="s">
+      <c r="B33" s="190" t="s">
         <v>155</v>
       </c>
-      <c r="C33" s="192">
+      <c r="C33" s="191">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="D33" s="191" t="s">
+        <v>156</v>
+      </c>
+      <c r="E33" s="192" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" s="193">
+        <v>4.5</v>
+      </c>
+      <c r="G33" s="194">
+        <v>135000.28</v>
+      </c>
+      <c r="H33" s="234">
+        <v>135000</v>
+      </c>
+      <c r="I33" s="195"/>
+      <c r="J33" s="196">
+        <f t="shared" si="1"/>
+        <v>0.27999999999883585</v>
+      </c>
+      <c r="K33" s="196"/>
+      <c r="L33" s="194">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M33" s="196">
+        <f t="shared" si="6"/>
+        <v>135000</v>
+      </c>
+      <c r="N33" s="197"/>
+      <c r="O33" s="198">
+        <f t="shared" si="7"/>
+        <v>135000.28</v>
+      </c>
+      <c r="P33" s="197">
+        <f t="shared" si="3"/>
+        <v>143100.28</v>
+      </c>
+      <c r="Q33" s="199">
+        <f t="shared" si="4"/>
+        <v>139050.28</v>
+      </c>
+      <c r="R33" s="60">
         <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="D33" s="192" t="s">
-        <v>156</v>
-      </c>
-      <c r="E33" s="193" t="s">
-        <v>157</v>
-      </c>
-      <c r="F33" s="194">
-        <v>4.5</v>
-      </c>
-      <c r="G33" s="195">
-        <v>135000</v>
-      </c>
-      <c r="H33" s="276">
-        <v>135000</v>
-      </c>
-      <c r="I33" s="196"/>
-      <c r="J33" s="197">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K33" s="197"/>
-      <c r="L33" s="195">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M33" s="197">
-        <f t="shared" si="5"/>
-        <v>135000</v>
-      </c>
-      <c r="N33" s="198"/>
-      <c r="O33" s="199">
-        <f t="shared" si="6"/>
-        <v>135000.28</v>
-      </c>
-      <c r="P33" s="198">
-        <f t="shared" si="2"/>
-        <v>143100.28</v>
-      </c>
-      <c r="Q33" s="200">
-        <f t="shared" si="3"/>
-        <v>139050.28</v>
-      </c>
-      <c r="R33" s="60">
-        <f t="shared" si="7"/>
         <v>0.28000000000000008</v>
       </c>
     </row>
@@ -7678,7 +7827,7 @@
         <v>158</v>
       </c>
       <c r="C34" s="120">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="D34" s="120" t="s">
@@ -7697,38 +7846,38 @@
       </c>
       <c r="I34" s="100"/>
       <c r="J34" s="101">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="101">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="K34" s="101">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="L34" s="98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M34" s="101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>93000</v>
       </c>
       <c r="N34" s="102">
         <v>0</v>
       </c>
       <c r="O34" s="126">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>93000.29</v>
       </c>
       <c r="P34" s="107">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>98580.29</v>
       </c>
       <c r="Q34" s="127">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>95790.29</v>
       </c>
       <c r="R34" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.29000000000000009</v>
       </c>
     </row>
@@ -7745,11 +7894,11 @@
       <c r="H35" s="139"/>
       <c r="I35" s="100"/>
       <c r="J35" s="101">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K35" s="101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L35" s="98"/>
@@ -7759,15 +7908,15 @@
       </c>
       <c r="O35" s="103"/>
       <c r="P35" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.3000000000000001</v>
       </c>
       <c r="Q35" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R35" s="60">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.3000000000000001</v>
       </c>
     </row>
@@ -7784,11 +7933,11 @@
       <c r="H36" s="99"/>
       <c r="I36" s="109"/>
       <c r="J36" s="110">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K36" s="101">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L36" s="108">
@@ -7796,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="110">
-        <f>RESUMEN!H$87*F36%</f>
+        <f>RESUMEN!H$91*F36%</f>
         <v>0</v>
       </c>
       <c r="N36" s="111">
@@ -7807,11 +7956,11 @@
         <v>0</v>
       </c>
       <c r="P36" s="102">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q36" s="104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R36" s="60"/>
@@ -7822,52 +7971,52 @@
       <c r="D37" s="114"/>
       <c r="E37" s="114"/>
       <c r="F37" s="122">
-        <f t="shared" ref="F37:Q37" si="9">SUM(F6:F36)</f>
+        <f t="shared" ref="F37:Q37" si="10">SUM(F6:F36)</f>
         <v>99.999999999999986</v>
       </c>
       <c r="G37" s="115">
-        <f t="shared" si="9"/>
-        <v>4584523.9899999993</v>
+        <f t="shared" si="10"/>
+        <v>3975837.3499999987</v>
       </c>
       <c r="H37" s="116">
-        <f t="shared" si="9"/>
-        <v>3745120.1399999997</v>
+        <f t="shared" si="10"/>
+        <v>3430553.54</v>
       </c>
       <c r="I37" s="115">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J37" s="116">
-        <f t="shared" si="9"/>
-        <v>839403.85</v>
+        <f t="shared" si="10"/>
+        <v>545283.81000000006</v>
       </c>
       <c r="K37" s="115">
-        <f t="shared" si="9"/>
-        <v>25206.587099999997</v>
+        <f t="shared" si="10"/>
+        <v>16443.900299999998</v>
       </c>
       <c r="L37" s="116">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M37" s="115">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3000000</v>
       </c>
       <c r="N37" s="116">
-        <f t="shared" si="9"/>
-        <v>91004</v>
+        <f t="shared" si="10"/>
+        <v>117004</v>
       </c>
       <c r="O37" s="117">
-        <f t="shared" si="9"/>
-        <v>3955618.3499999987</v>
+        <f t="shared" si="10"/>
+        <v>3678734.3499999987</v>
       </c>
       <c r="P37" s="117">
-        <f t="shared" si="9"/>
-        <v>4192958.6499999985</v>
+        <f t="shared" si="10"/>
+        <v>3899461.6499999985</v>
       </c>
       <c r="Q37" s="117">
-        <f t="shared" si="9"/>
-        <v>4074285.3499999987</v>
+        <f t="shared" si="10"/>
+        <v>3789096.3499999987</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -7884,95 +8033,95 @@
       <c r="Q39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="244" t="s">
+      <c r="D40" s="270" t="s">
         <v>163</v>
       </c>
-      <c r="E40" s="234"/>
-      <c r="F40" s="234"/>
-      <c r="G40" s="234"/>
-      <c r="H40" s="234"/>
-      <c r="I40" s="234"/>
-      <c r="J40" s="234"/>
-      <c r="K40" s="234"/>
-      <c r="L40" s="234"/>
-      <c r="M40" s="234"/>
-      <c r="N40" s="234"/>
-      <c r="O40" s="234"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="245"/>
+      <c r="N40" s="245"/>
+      <c r="O40" s="245"/>
       <c r="Q40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="234"/>
-      <c r="E41" s="234"/>
-      <c r="F41" s="234"/>
-      <c r="G41" s="234"/>
-      <c r="H41" s="234"/>
-      <c r="I41" s="234"/>
-      <c r="J41" s="234"/>
-      <c r="K41" s="234"/>
-      <c r="L41" s="234"/>
-      <c r="M41" s="234"/>
-      <c r="N41" s="234"/>
-      <c r="O41" s="234"/>
+      <c r="D41" s="245"/>
+      <c r="E41" s="245"/>
+      <c r="F41" s="245"/>
+      <c r="G41" s="245"/>
+      <c r="H41" s="245"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
+      <c r="M41" s="245"/>
+      <c r="N41" s="245"/>
+      <c r="O41" s="245"/>
       <c r="Q41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
-      <c r="I42" s="234"/>
-      <c r="J42" s="234"/>
-      <c r="K42" s="234"/>
-      <c r="L42" s="234"/>
-      <c r="M42" s="234"/>
-      <c r="N42" s="234"/>
-      <c r="O42" s="234"/>
+      <c r="D42" s="245"/>
+      <c r="E42" s="245"/>
+      <c r="F42" s="245"/>
+      <c r="G42" s="245"/>
+      <c r="H42" s="245"/>
+      <c r="I42" s="245"/>
+      <c r="J42" s="245"/>
+      <c r="K42" s="245"/>
+      <c r="L42" s="245"/>
+      <c r="M42" s="245"/>
+      <c r="N42" s="245"/>
+      <c r="O42" s="245"/>
       <c r="Q42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="234"/>
-      <c r="E43" s="234"/>
-      <c r="F43" s="234"/>
-      <c r="G43" s="234"/>
-      <c r="H43" s="234"/>
-      <c r="I43" s="234"/>
-      <c r="J43" s="234"/>
-      <c r="K43" s="234"/>
-      <c r="L43" s="234"/>
-      <c r="M43" s="234"/>
-      <c r="N43" s="234"/>
-      <c r="O43" s="234"/>
+      <c r="D43" s="245"/>
+      <c r="E43" s="245"/>
+      <c r="F43" s="245"/>
+      <c r="G43" s="245"/>
+      <c r="H43" s="245"/>
+      <c r="I43" s="245"/>
+      <c r="J43" s="245"/>
+      <c r="K43" s="245"/>
+      <c r="L43" s="245"/>
+      <c r="M43" s="245"/>
+      <c r="N43" s="245"/>
+      <c r="O43" s="245"/>
       <c r="Q43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="234"/>
-      <c r="E44" s="234"/>
-      <c r="F44" s="234"/>
-      <c r="G44" s="234"/>
-      <c r="H44" s="234"/>
-      <c r="I44" s="234"/>
-      <c r="J44" s="234"/>
-      <c r="K44" s="234"/>
-      <c r="L44" s="234"/>
-      <c r="M44" s="234"/>
-      <c r="N44" s="234"/>
-      <c r="O44" s="234"/>
+      <c r="D44" s="245"/>
+      <c r="E44" s="245"/>
+      <c r="F44" s="245"/>
+      <c r="G44" s="245"/>
+      <c r="H44" s="245"/>
+      <c r="I44" s="245"/>
+      <c r="J44" s="245"/>
+      <c r="K44" s="245"/>
+      <c r="L44" s="245"/>
+      <c r="M44" s="245"/>
+      <c r="N44" s="245"/>
+      <c r="O44" s="245"/>
       <c r="Q44" s="1"/>
     </row>
     <row r="45" spans="1:18" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="234"/>
-      <c r="E45" s="234"/>
-      <c r="F45" s="234"/>
-      <c r="G45" s="234"/>
-      <c r="H45" s="234"/>
-      <c r="I45" s="234"/>
-      <c r="J45" s="234"/>
-      <c r="K45" s="234"/>
-      <c r="L45" s="234"/>
-      <c r="M45" s="234"/>
-      <c r="N45" s="234"/>
-      <c r="O45" s="234"/>
+      <c r="D45" s="245"/>
+      <c r="E45" s="245"/>
+      <c r="F45" s="245"/>
+      <c r="G45" s="245"/>
+      <c r="H45" s="245"/>
+      <c r="I45" s="245"/>
+      <c r="J45" s="245"/>
+      <c r="K45" s="245"/>
+      <c r="L45" s="245"/>
+      <c r="M45" s="245"/>
+      <c r="N45" s="245"/>
+      <c r="O45" s="245"/>
       <c r="Q45" s="1"/>
     </row>
     <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
